--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -2189,26 +2189,20 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J27" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0.449208825826645</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHCCPVEA156NRUG</t>
@@ -2420,26 +2414,20 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J30" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>-0.301709741353989</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHMCPVEA156NRUG</t>
@@ -2724,26 +2712,20 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J34" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>1954-01-01</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="n">
-        <v>0.0518108420073986</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CTFPPPVEA669NRUG</t>
@@ -3095,26 +3077,20 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J39" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="n">
-        <v>16.533233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDAI02VEA643NWDB</t>
@@ -3764,26 +3740,20 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J48" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>1963-01-01</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="n">
-        <v>0.193082</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI03VEA156NWDB</t>
@@ -3843,26 +3813,20 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J49" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="M49" s="6" t="n">
-        <v>69.07484000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="n"/>
       <c r="N49" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI04VEA156NWDB</t>
@@ -4147,26 +4111,20 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J53" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M53" s="6" t="n">
-        <v>0.0001330999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="n"/>
       <c r="N53" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI09VEA156NWDB</t>
@@ -4615,26 +4573,20 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J59" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>1996-01-01</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M59" s="6" t="n">
-        <v>1.253404</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr"/>
+      <c r="M59" s="4" t="n"/>
       <c r="N59" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM03VEA156NWDB</t>
@@ -4694,26 +4646,20 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J60" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>1996-01-01</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M60" s="6" t="n">
-        <v>20.26552</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr"/>
+      <c r="M60" s="4" t="n"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM04VEA156NWDB</t>
@@ -4773,26 +4719,20 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J61" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>1980-01-01</t>
-        </is>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M61" s="6" t="n">
-        <v>9.759254</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM05VEA156NWDB</t>
@@ -5241,26 +5181,20 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J67" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M67" s="6" t="n">
-        <v>2.437905</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
+      <c r="M67" s="4" t="n"/>
       <c r="N67" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI01VEA156NWDB</t>
@@ -5320,26 +5254,20 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J68" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M68" s="6" t="n">
-        <v>6.326667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI02VEA156NWDB</t>
@@ -5472,26 +5400,20 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J70" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M70" s="6" t="n">
-        <v>6.681727</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="n"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI04VEA156NWDB</t>
@@ -5551,26 +5473,20 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J71" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M71" s="6" t="n">
-        <v>1.153893</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="n"/>
       <c r="N71" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI05VEA156NWDB</t>
@@ -6524,26 +6440,20 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J84" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="K84" s="4" t="inlineStr">
-        <is>
-          <t>1972-01-01</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M84" s="6" t="n">
-        <v>-0.5978945</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="n"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI08VEA156NWDB</t>
@@ -6603,26 +6513,20 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J85" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>1972-01-01</t>
-        </is>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M85" s="6" t="n">
-        <v>10.83362</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K85" s="4" t="inlineStr"/>
+      <c r="L85" s="4" t="inlineStr"/>
+      <c r="M85" s="4" t="n"/>
       <c r="N85" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI09VEA156NWDB</t>
@@ -6834,26 +6738,20 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J88" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="K88" s="4" t="inlineStr">
-        <is>
-          <t>1983-01-01</t>
-        </is>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M88" s="6" t="n">
-        <v>5.584377</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K88" s="4" t="inlineStr"/>
+      <c r="L88" s="4" t="inlineStr"/>
+      <c r="M88" s="4" t="n"/>
       <c r="N88" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI12VEA156NWDB</t>
@@ -7059,26 +6957,20 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J91" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M91" s="6" t="n">
-        <v>1.231569</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="n"/>
       <c r="N91" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOM01VEA644NWDB</t>
@@ -7217,26 +7109,20 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J93" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M93" s="6" t="n">
-        <v>0.83999997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K93" s="4" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr"/>
+      <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI02VEA156NWDB</t>
@@ -7296,26 +7182,20 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J94" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M94" s="6" t="n">
-        <v>10.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI03VEA156NWDB</t>
@@ -7375,26 +7255,20 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J95" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M95" s="6" t="n">
-        <v>63.24106999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K95" s="4" t="inlineStr"/>
+      <c r="L95" s="4" t="inlineStr"/>
+      <c r="M95" s="4" t="n"/>
       <c r="N95" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI04VEA156NWDB</t>
@@ -7899,7 +7773,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="n">
-        <v>6678</v>
+        <v>6687</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -7908,11 +7782,11 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>789.6875</v>
+        <v>830.41</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
@@ -8423,26 +8297,20 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J109" s="5" t="n">
-        <v>498</v>
-      </c>
-      <c r="K109" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M109" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K109" s="4" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr"/>
+      <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTAGCYVALCHG32719</t>
@@ -8794,26 +8662,20 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I114" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J114" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K114" s="4" t="inlineStr">
-        <is>
-          <t>1984-12-01</t>
-        </is>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M114" s="5" t="n">
-        <v>3974</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K114" s="4" t="inlineStr"/>
+      <c r="L114" s="4" t="inlineStr"/>
+      <c r="M114" s="4" t="n"/>
       <c r="N114" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTEQTYPOS32719</t>
@@ -9463,26 +9325,20 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J123" s="5" t="n">
-        <v>281</v>
-      </c>
-      <c r="K123" s="4" t="inlineStr">
-        <is>
-          <t>2003-02-01</t>
-        </is>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M123" s="5" t="n">
-        <v>297</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K123" s="4" t="inlineStr"/>
+      <c r="L123" s="4" t="inlineStr"/>
+      <c r="M123" s="4" t="n"/>
       <c r="N123" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORSTTREASPOS32719</t>
@@ -10892,26 +10748,20 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J142" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K142" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M142" s="5" t="n">
-        <v>188</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K142" s="4" t="inlineStr"/>
+      <c r="L142" s="4" t="inlineStr"/>
+      <c r="M142" s="4" t="n"/>
       <c r="N142" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ICBUSEASEXQVEN</t>
@@ -11640,26 +11490,20 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I152" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J152" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="K152" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M152" s="5" t="n">
-        <v>2397</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K152" s="4" t="inlineStr"/>
+      <c r="L152" s="4" t="inlineStr"/>
+      <c r="M152" s="4" t="n"/>
       <c r="N152" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSAMRINIVE</t>
@@ -12017,26 +11861,20 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J157" s="5" t="n">
-        <v>214</v>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M157" s="5" t="n">
-        <v>15950</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K157" s="4" t="inlineStr"/>
+      <c r="L157" s="4" t="inlineStr"/>
+      <c r="M157" s="4" t="n"/>
       <c r="N157" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMRIAOVE</t>
@@ -12540,26 +12378,20 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J164" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="K164" s="4" t="inlineStr">
-        <is>
-          <t>1993-07-01</t>
-        </is>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M164" s="6" t="n">
-        <v>-1.12602</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K164" s="4" t="inlineStr"/>
+      <c r="L164" s="4" t="inlineStr"/>
+      <c r="M164" s="4" t="n"/>
       <c r="N164" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGGGAMNINIVE</t>
@@ -12692,26 +12524,20 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I166" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J166" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="K166" s="4" t="inlineStr">
-        <is>
-          <t>1993-07-01</t>
-        </is>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>2014-10-01</t>
-        </is>
-      </c>
-      <c r="M166" s="6" t="n">
-        <v>-1.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K166" s="4" t="inlineStr"/>
+      <c r="L166" s="4" t="inlineStr"/>
+      <c r="M166" s="4" t="n"/>
       <c r="N166" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGNFAMNINIVE</t>
@@ -13355,26 +13181,20 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J175" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K175" s="4" t="inlineStr">
-        <is>
-          <t>1990-10-01</t>
-        </is>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>1997-04-01</t>
-        </is>
-      </c>
-      <c r="M175" s="6" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K175" s="4" t="inlineStr"/>
+      <c r="L175" s="4" t="inlineStr"/>
+      <c r="M175" s="4" t="n"/>
       <c r="N175" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIAOVE</t>
@@ -13434,26 +13254,20 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J176" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K176" s="4" t="inlineStr">
-        <is>
-          <t>1993-10-01</t>
-        </is>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="M176" s="6" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K176" s="4" t="inlineStr"/>
+      <c r="L176" s="4" t="inlineStr"/>
+      <c r="M176" s="4" t="n"/>
       <c r="N176" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIGIVE</t>
@@ -13513,26 +13327,20 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J177" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K177" s="4" t="inlineStr">
-        <is>
-          <t>1993-10-01</t>
-        </is>
-      </c>
-      <c r="L177" s="4" t="inlineStr">
-        <is>
-          <t>1997-07-01</t>
-        </is>
-      </c>
-      <c r="M177" s="6" t="n">
-        <v>-0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K177" s="4" t="inlineStr"/>
+      <c r="L177" s="4" t="inlineStr"/>
+      <c r="M177" s="4" t="n"/>
       <c r="N177" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAINIVE</t>
@@ -14425,26 +14233,20 @@
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J189" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K189" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L189" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M189" s="6" t="n">
-        <v>24.52833168</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K189" s="4" t="inlineStr"/>
+      <c r="L189" s="4" t="inlineStr"/>
+      <c r="M189" s="4" t="n"/>
       <c r="N189" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KIPPPGVEA156NUPN</t>
@@ -16274,26 +16076,20 @@
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I214" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J214" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K214" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L214" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M214" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K214" s="4" t="inlineStr"/>
+      <c r="L214" s="4" t="inlineStr"/>
+      <c r="M214" s="4" t="n"/>
       <c r="N214" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA475SCEN</t>
@@ -17016,26 +16812,20 @@
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I224" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J224" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K224" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L224" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M224" s="5" t="n">
-        <v>3888969</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K224" s="4" t="inlineStr"/>
+      <c r="L224" s="4" t="inlineStr"/>
+      <c r="M224" s="4" t="n"/>
       <c r="N224" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NJVENA052SCEN</t>
@@ -17168,26 +16958,20 @@
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I226" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J226" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K226" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L226" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M226" s="5" t="n">
-        <v>743939</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K226" s="4" t="inlineStr"/>
+      <c r="L226" s="4" t="inlineStr"/>
+      <c r="M226" s="4" t="n"/>
       <c r="N226" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NMVENA052SCEN</t>
@@ -17983,26 +17767,20 @@
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I237" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J237" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K237" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L237" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M237" s="6" t="n">
-        <v>45.86565346</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K237" s="4" t="inlineStr"/>
+      <c r="L237" s="4" t="inlineStr"/>
+      <c r="M237" s="4" t="n"/>
       <c r="N237" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OPENCPVEA156NUPN</t>
@@ -18135,26 +17913,20 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I239" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J239" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K239" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L239" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M239" s="5" t="n">
-        <v>197417</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K239" s="4" t="inlineStr"/>
+      <c r="L239" s="4" t="inlineStr"/>
+      <c r="M239" s="4" t="n"/>
       <c r="N239" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ORVENA052SCEN</t>
@@ -18506,26 +18278,20 @@
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I244" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I244" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J244" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K244" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L244" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M244" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K244" s="4" t="inlineStr"/>
+      <c r="L244" s="4" t="inlineStr"/>
+      <c r="M244" s="4" t="n"/>
       <c r="N244" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVETOTAL</t>
@@ -18585,26 +18351,20 @@
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I245" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J245" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K245" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L245" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M245" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K245" s="4" t="inlineStr"/>
+      <c r="L245" s="4" t="inlineStr"/>
+      <c r="M245" s="4" t="n"/>
       <c r="N245" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEUTILITY</t>
@@ -18810,26 +18570,20 @@
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I248" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J248" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K248" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L248" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M248" s="6" t="n">
-        <v>11809.94057</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K248" s="4" t="inlineStr"/>
+      <c r="L248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="n"/>
       <c r="N248" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PC2GDPVEA620NUPN</t>
@@ -19041,26 +18795,20 @@
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I251" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J251" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K251" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L251" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M251" s="6" t="n">
-        <v>25.36032612</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K251" s="4" t="inlineStr"/>
+      <c r="L251" s="4" t="inlineStr"/>
+      <c r="M251" s="4" t="n"/>
       <c r="N251" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PGD2USVEA621NUPN</t>
@@ -19199,26 +18947,20 @@
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I253" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J253" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K253" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L253" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M253" s="6" t="n">
-        <v>121.3461635</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K253" s="4" t="inlineStr"/>
+      <c r="L253" s="4" t="inlineStr"/>
+      <c r="M253" s="4" t="n"/>
       <c r="N253" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PL2GDPVEA621NUPN</t>
@@ -19357,26 +19099,20 @@
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I255" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J255" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K255" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L255" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M255" s="6" t="n">
-        <v>23.2163643183614</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K255" s="4" t="inlineStr"/>
+      <c r="L255" s="4" t="inlineStr"/>
+      <c r="M255" s="4" t="n"/>
       <c r="N255" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLGCPPVEA670NRUG</t>
@@ -19740,26 +19476,20 @@
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I260" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I260" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J260" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K260" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L260" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M260" s="6" t="n">
-        <v>0.610256195068359</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K260" s="4" t="inlineStr"/>
+      <c r="L260" s="4" t="inlineStr"/>
+      <c r="M260" s="4" t="n"/>
       <c r="N260" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLMCPPVEA670NRUG</t>
@@ -19819,26 +19549,20 @@
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I261" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J261" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K261" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L261" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M261" s="6" t="n">
-        <v>121.4234463</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K261" s="4" t="inlineStr"/>
+      <c r="L261" s="4" t="inlineStr"/>
+      <c r="M261" s="4" t="n"/>
       <c r="N261" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOCONVEA622NUPN</t>
@@ -19898,26 +19622,20 @@
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I262" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I262" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J262" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K262" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L262" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M262" s="6" t="n">
-        <v>122.0413712</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K262" s="4" t="inlineStr"/>
+      <c r="L262" s="4" t="inlineStr"/>
+      <c r="M262" s="4" t="n"/>
       <c r="N262" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOGDPVEA621NUPN</t>
@@ -20050,26 +19768,20 @@
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I264" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J264" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K264" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L264" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M264" s="6" t="n">
-        <v>119.0453568</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K264" s="4" t="inlineStr"/>
+      <c r="L264" s="4" t="inlineStr"/>
+      <c r="M264" s="4" t="n"/>
       <c r="N264" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOINVVEA624NUPN</t>
@@ -20520,26 +20232,20 @@
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I270" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J270" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K270" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L270" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M270" s="6" t="n">
-        <v>320634.9337</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K270" s="4" t="inlineStr"/>
+      <c r="L270" s="4" t="inlineStr"/>
+      <c r="M270" s="4" t="n"/>
       <c r="N270" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PPPGDPVEA619NUPN</t>
@@ -21541,26 +21247,20 @@
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I283" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J283" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K283" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L283" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M283" s="6" t="n">
-        <v>25811.10218</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K283" s="4" t="inlineStr"/>
+      <c r="L283" s="4" t="inlineStr"/>
+      <c r="M283" s="4" t="n"/>
       <c r="N283" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPTEVEA629NUPN</t>
@@ -21772,26 +21472,20 @@
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I286" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J286" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K286" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L286" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M286" s="6" t="n">
-        <v>19511.40489</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K286" s="4" t="inlineStr"/>
+      <c r="L286" s="4" t="inlineStr"/>
+      <c r="M286" s="4" t="n"/>
       <c r="N286" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPWOVEA627NUPN</t>
@@ -22374,26 +22068,20 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I294" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I294" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J294" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K294" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L294" s="4" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="M294" s="5" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K294" s="4" t="inlineStr"/>
+      <c r="L294" s="4" t="inlineStr"/>
+      <c r="M294" s="4" t="n"/>
       <c r="N294" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SDVENA475SCEN</t>
@@ -22605,26 +22293,20 @@
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I297" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I297" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J297" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="K297" s="4" t="inlineStr">
-        <is>
-          <t>1971-01-01</t>
-        </is>
-      </c>
-      <c r="L297" s="4" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M297" s="6" t="n">
-        <v>1.0806200504303</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K297" s="4" t="inlineStr"/>
+      <c r="L297" s="4" t="inlineStr"/>
+      <c r="M297" s="4" t="n"/>
       <c r="N297" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRSECOFMZSVEN</t>
@@ -22684,26 +22366,20 @@
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I298" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J298" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K298" s="4" t="inlineStr">
-        <is>
-          <t>1986-01-01</t>
-        </is>
-      </c>
-      <c r="L298" s="4" t="inlineStr">
-        <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="M298" s="6" t="n">
-        <v>1.40991997718811</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K298" s="4" t="inlineStr"/>
+      <c r="L298" s="4" t="inlineStr"/>
+      <c r="M298" s="4" t="n"/>
       <c r="N298" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRTERTFMZSVEN</t>
@@ -23626,26 +23302,20 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I310" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I310" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J310" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="K310" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L310" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="M310" s="6" t="n">
-        <v>24.9159954154898</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K310" s="4" t="inlineStr"/>
+      <c r="L310" s="4" t="inlineStr"/>
+      <c r="M310" s="4" t="n"/>
       <c r="N310" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPPOP0014TOZSVEN</t>
@@ -25195,26 +24865,20 @@
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I331" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I331" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J331" s="5" t="n">
-        <v>387</v>
-      </c>
-      <c r="K331" s="4" t="inlineStr">
-        <is>
-          <t>1994-04-01</t>
-        </is>
-      </c>
-      <c r="L331" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M331" s="5" t="n">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K331" s="4" t="inlineStr"/>
+      <c r="L331" s="4" t="inlineStr"/>
+      <c r="M331" s="4" t="n"/>
       <c r="N331" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALNET32719</t>
@@ -25347,26 +25011,20 @@
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I333" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I333" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J333" s="5" t="n">
-        <v>387</v>
-      </c>
-      <c r="K333" s="4" t="inlineStr">
-        <is>
-          <t>1994-04-01</t>
-        </is>
-      </c>
-      <c r="L333" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M333" s="5" t="n">
-        <v>-238</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K333" s="4" t="inlineStr"/>
+      <c r="L333" s="4" t="inlineStr"/>
+      <c r="M333" s="4" t="n"/>
       <c r="N333" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALVALCHG32719</t>
@@ -25499,26 +25157,20 @@
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I335" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I335" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J335" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K335" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L335" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M335" s="5" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K335" s="4" t="inlineStr"/>
+      <c r="L335" s="4" t="inlineStr"/>
+      <c r="M335" s="4" t="n"/>
       <c r="N335" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/UTVENA475SCEN</t>
@@ -25870,26 +25522,20 @@
       </c>
       <c r="H340" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I340" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I340" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J340" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K340" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L340" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M340" s="5" t="n">
-        <v>10429</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K340" s="4" t="inlineStr"/>
+      <c r="L340" s="4" t="inlineStr"/>
+      <c r="M340" s="4" t="n"/>
       <c r="N340" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCACNUM</t>
@@ -26095,26 +25741,20 @@
       </c>
       <c r="H343" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I343" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I343" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J343" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K343" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L343" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M343" s="5" t="n">
-        <v>31695711</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K343" s="4" t="inlineStr"/>
+      <c r="L343" s="4" t="inlineStr"/>
+      <c r="M343" s="4" t="n"/>
       <c r="N343" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODCNUM</t>
@@ -26320,26 +25960,20 @@
       </c>
       <c r="H346" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I346" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I346" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J346" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K346" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L346" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M346" s="5" t="n">
-        <v>1769451</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K346" s="4" t="inlineStr"/>
+      <c r="L346" s="4" t="inlineStr"/>
+      <c r="M346" s="4" t="n"/>
       <c r="N346" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAOFILNNUM</t>
@@ -26910,26 +26544,20 @@
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I354" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I354" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J354" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K354" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L354" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M354" s="6" t="n">
-        <v>0.130378096</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K354" s="4" t="inlineStr"/>
+      <c r="L354" s="4" t="inlineStr"/>
+      <c r="M354" s="4" t="n"/>
       <c r="N354" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODMFKNUM</t>
@@ -27281,26 +26909,20 @@
       </c>
       <c r="H359" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I359" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I359" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J359" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K359" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L359" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M359" s="6" t="n">
-        <v>24601704.6666667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K359" s="4" t="inlineStr"/>
+      <c r="L359" s="4" t="inlineStr"/>
+      <c r="M359" s="4" t="n"/>
       <c r="N359" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCHPENUM</t>
@@ -27506,26 +27128,20 @@
       </c>
       <c r="H362" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I362" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I362" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J362" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K362" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L362" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M362" s="6" t="n">
-        <v>66.83665774000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K362" s="4" t="inlineStr"/>
+      <c r="L362" s="4" t="inlineStr"/>
+      <c r="M362" s="4" t="n"/>
       <c r="N362" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPNUM</t>
@@ -27731,26 +27347,20 @@
       </c>
       <c r="H365" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I365" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I365" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J365" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K365" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L365" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M365" s="5" t="n">
-        <v>26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K365" s="4" t="inlineStr"/>
+      <c r="L365" s="4" t="inlineStr"/>
+      <c r="M365" s="4" t="n"/>
       <c r="N365" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIODCNUM</t>
@@ -28029,26 +27639,20 @@
       </c>
       <c r="H369" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I369" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I369" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J369" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K369" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L369" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M369" s="6" t="n">
-        <v>68.50582168130001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K369" s="4" t="inlineStr"/>
+      <c r="L369" s="4" t="inlineStr"/>
+      <c r="M369" s="4" t="n"/>
       <c r="N369" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCGGDPPT</t>
@@ -28254,26 +27858,20 @@
       </c>
       <c r="H372" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I372" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I372" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J372" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K372" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L372" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M372" s="6" t="n">
-        <v>21.4396202031903</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K372" s="4" t="inlineStr"/>
+      <c r="L372" s="4" t="inlineStr"/>
+      <c r="M372" s="4" t="n"/>
       <c r="N372" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCSGGDPPT</t>
@@ -28552,26 +28150,20 @@
       </c>
       <c r="H376" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I376" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I376" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J376" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K376" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L376" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M376" s="6" t="n">
-        <v>37322701822.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K376" s="4" t="inlineStr"/>
+      <c r="L376" s="4" t="inlineStr"/>
+      <c r="M376" s="4" t="n"/>
       <c r="N376" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODMFXDC</t>
@@ -28850,26 +28442,20 @@
       </c>
       <c r="H380" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I380" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I380" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J380" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K380" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L380" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M380" s="6" t="n">
-        <v>1078.0378178439</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K380" s="4" t="inlineStr"/>
+      <c r="L380" s="4" t="inlineStr"/>
+      <c r="M380" s="4" t="n"/>
       <c r="N380" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODCANUM</t>
@@ -29300,26 +28886,20 @@
       </c>
       <c r="H386" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I386" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I386" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J386" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K386" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L386" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M386" s="6" t="n">
-        <v>7404689.58333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K386" s="4" t="inlineStr"/>
+      <c r="L386" s="4" t="inlineStr"/>
+      <c r="M386" s="4" t="n"/>
       <c r="N386" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHPENUM</t>
@@ -29598,26 +29178,20 @@
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I390" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I390" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J390" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K390" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L390" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M390" s="6" t="n">
-        <v>37.8908354029</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K390" s="4" t="inlineStr"/>
+      <c r="L390" s="4" t="inlineStr"/>
+      <c r="M390" s="4" t="n"/>
       <c r="N390" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCGGDPPT</t>
@@ -30048,26 +29622,20 @@
       </c>
       <c r="H396" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I396" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I396" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J396" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K396" s="4" t="inlineStr">
-        <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="L396" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M396" s="5" t="n">
-        <v>10753000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K396" s="4" t="inlineStr"/>
+      <c r="L396" s="4" t="inlineStr"/>
+      <c r="M396" s="4" t="n"/>
       <c r="N396" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFSXDC</t>
@@ -30200,26 +29768,20 @@
       </c>
       <c r="H398" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I398" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I398" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J398" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K398" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L398" s="4" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="M398" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K398" s="4" t="inlineStr"/>
+      <c r="L398" s="4" t="inlineStr"/>
+      <c r="M398" s="4" t="n"/>
       <c r="N398" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VIVENA475SCEN</t>
@@ -30942,26 +30504,20 @@
       </c>
       <c r="H408" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I408" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I408" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J408" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="K408" s="4" t="inlineStr">
-        <is>
-          <t>1996-01-01</t>
-        </is>
-      </c>
-      <c r="L408" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M408" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K408" s="4" t="inlineStr"/>
+      <c r="L408" s="4" t="inlineStr"/>
+      <c r="M408" s="4" t="n"/>
       <c r="N408" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WUPIVEN</t>
@@ -31094,26 +30650,20 @@
       </c>
       <c r="H410" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I410" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I410" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J410" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="K410" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L410" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M410" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K410" s="4" t="inlineStr"/>
+      <c r="L410" s="4" t="inlineStr"/>
+      <c r="M410" s="4" t="n"/>
       <c r="N410" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WVVENA475SCEN</t>
@@ -31440,7 +30990,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -31497,7 +31047,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>171</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -31507,7 +31057,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>19477</v>
+        <v>14774</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -2712,20 +2712,26 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="4" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>1954-01-01</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.0518108420073986</v>
+      </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CTFPPPVEA669NRUG</t>
@@ -4670,20 +4676,26 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr"/>
       <c r="J60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr"/>
-      <c r="M60" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>20.26552</v>
+      </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM04VEA156NWDB</t>
@@ -4743,20 +4755,26 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr"/>
       <c r="J61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr"/>
-      <c r="M61" s="4" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="n">
+        <v>9.759254</v>
+      </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM05VEA156NWDB</t>
@@ -5503,20 +5521,26 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr"/>
       <c r="J71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="4" t="inlineStr"/>
-      <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="n">
+        <v>1.153893</v>
+      </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI05VEA156NWDB</t>
@@ -6549,20 +6573,26 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr"/>
       <c r="J85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="4" t="inlineStr"/>
-      <c r="L85" s="4" t="inlineStr"/>
-      <c r="M85" s="4" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>1972-01-01</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="n">
+        <v>10.83362</v>
+      </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI09VEA156NWDB</t>
@@ -7815,7 +7845,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="n">
-        <v>6697</v>
+        <v>6702</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -7824,11 +7854,11 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>853.5232999999999</v>
+        <v>864.3948</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
@@ -7973,7 +8003,7 @@
       </c>
       <c r="I104" s="4" t="inlineStr"/>
       <c r="J104" s="5" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
@@ -7982,11 +8012,11 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M104" s="6" t="n">
-        <v>501.024042</v>
+        <v>646.199606</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
@@ -13684,7 +13714,7 @@
       </c>
       <c r="I181" s="4" t="inlineStr"/>
       <c r="J181" s="5" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
@@ -13693,11 +13723,11 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M181" s="6" t="n">
-        <v>1661.795998</v>
+        <v>1710.215481</v>
       </c>
       <c r="N181" s="4" t="inlineStr">
         <is>
@@ -14293,20 +14323,26 @@
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr"/>
       <c r="J189" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" s="4" t="inlineStr"/>
-      <c r="L189" s="4" t="inlineStr"/>
-      <c r="M189" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M189" s="6" t="n">
+        <v>24.52833168</v>
+      </c>
       <c r="N189" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KIPPPGVEA156NUPN</t>
@@ -18338,20 +18374,26 @@
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I244" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I244" s="4" t="inlineStr"/>
       <c r="J244" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K244" s="4" t="inlineStr"/>
-      <c r="L244" s="4" t="inlineStr"/>
-      <c r="M244" s="4" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L244" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M244" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N244" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVETOTAL</t>
@@ -18855,20 +18897,26 @@
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I251" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr"/>
       <c r="J251" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K251" s="4" t="inlineStr"/>
-      <c r="L251" s="4" t="inlineStr"/>
-      <c r="M251" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L251" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M251" s="6" t="n">
+        <v>25.36032612</v>
+      </c>
       <c r="N251" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PGD2USVEA621NUPN</t>
@@ -19165,20 +19213,26 @@
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I255" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr"/>
       <c r="J255" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K255" s="4" t="inlineStr"/>
-      <c r="L255" s="4" t="inlineStr"/>
-      <c r="M255" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L255" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M255" s="6" t="n">
+        <v>23.2163643183614</v>
+      </c>
       <c r="N255" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLGCPPVEA670NRUG</t>
@@ -19846,20 +19900,26 @@
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I264" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="inlineStr"/>
       <c r="J264" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K264" s="4" t="inlineStr"/>
-      <c r="L264" s="4" t="inlineStr"/>
-      <c r="M264" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L264" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M264" s="6" t="n">
+        <v>119.0453568</v>
+      </c>
       <c r="N264" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOINVVEA624NUPN</t>
@@ -26038,20 +26098,26 @@
       </c>
       <c r="H346" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I346" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I346" s="4" t="inlineStr"/>
       <c r="J346" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K346" s="4" t="inlineStr"/>
-      <c r="L346" s="4" t="inlineStr"/>
-      <c r="M346" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K346" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L346" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M346" s="5" t="n">
+        <v>1769451</v>
+      </c>
       <c r="N346" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAOFILNNUM</t>
@@ -28526,20 +28592,26 @@
       </c>
       <c r="H380" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I380" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I380" s="4" t="inlineStr"/>
       <c r="J380" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K380" s="4" t="inlineStr"/>
-      <c r="L380" s="4" t="inlineStr"/>
-      <c r="M380" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K380" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L380" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M380" s="6" t="n">
+        <v>1078.0378178439</v>
+      </c>
       <c r="N380" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODCANUM</t>
@@ -31080,7 +31152,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -31137,7 +31209,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
@@ -31147,7 +31219,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>15905</v>
+        <v>16411</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -681,20 +681,26 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>83990</v>
+      </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/AKVENA052SCEN</t>
@@ -827,20 +833,26 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1063662</v>
+      </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ALVENA052SCEN</t>
@@ -973,20 +985,26 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>273623</v>
+      </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ARVENA052SCEN</t>
@@ -1271,20 +1289,26 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/AZVENA475SCEN</t>
@@ -1502,20 +1526,26 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>14700660</v>
+      </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CAVENA052SCEN</t>
@@ -2116,20 +2146,26 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/COVENA475SCEN</t>
@@ -2189,20 +2225,26 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0.449208825826645</v>
+      </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHCCPVEA156NRUG</t>
@@ -2414,20 +2456,26 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>-0.301709741353989</v>
+      </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHMCPVEA156NRUG</t>
@@ -2487,20 +2535,26 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>-0.0894852876663208</v>
+      </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHRCPVEA156NRUG</t>
@@ -2937,20 +2991,26 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="4" t="inlineStr"/>
-      <c r="M37" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>375897</v>
+      </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DCVENA052SCEN</t>
@@ -3308,20 +3368,26 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr"/>
       <c r="J42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>84.03367</v>
+      </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDAI05VEA156NWDB</t>
@@ -3600,20 +3666,26 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr"/>
       <c r="J46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr"/>
-      <c r="M46" s="4" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>39.51449</v>
+      </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI01VEA156NWDB</t>
@@ -3831,20 +3903,26 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr"/>
-      <c r="M49" s="4" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>69.07484000000001</v>
+      </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI04VEA156NWDB</t>
@@ -4208,20 +4286,26 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr"/>
       <c r="J54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="4" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0.0031524</v>
+      </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI10VEA156NWDB</t>
@@ -5071,20 +5155,26 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr"/>
       <c r="J65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="4" t="inlineStr"/>
-      <c r="L65" s="4" t="inlineStr"/>
-      <c r="M65" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="n">
+        <v>0.0009455000000000001</v>
+      </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM09VEA156NWDB</t>
@@ -5302,20 +5392,26 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr"/>
       <c r="J68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="4" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="n">
+        <v>6.326667</v>
+      </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI02VEA156NWDB</t>
@@ -5448,20 +5544,26 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr"/>
       <c r="J70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="n">
+        <v>6.681727</v>
+      </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI04VEA156NWDB</t>
@@ -5673,20 +5775,26 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr"/>
       <c r="J73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="4" t="inlineStr"/>
-      <c r="L73" s="4" t="inlineStr"/>
-      <c r="M73" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M73" s="6" t="n">
+        <v>77.95326</v>
+      </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI07VEA156NWDB</t>
@@ -5825,20 +5933,26 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr"/>
       <c r="J75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="4" t="inlineStr"/>
-      <c r="L75" s="4" t="inlineStr"/>
-      <c r="M75" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>2002-01-01</t>
+        </is>
+      </c>
+      <c r="M75" s="6" t="n">
+        <v>2.23138</v>
+      </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEM01VEA156NWDB</t>
@@ -6123,20 +6237,26 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr"/>
       <c r="J79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="4" t="inlineStr"/>
-      <c r="L79" s="4" t="inlineStr"/>
-      <c r="M79" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="n">
+        <v>0.722</v>
+      </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI03VEA066NWDB</t>
@@ -6196,20 +6316,26 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr"/>
       <c r="J80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="4" t="inlineStr"/>
-      <c r="L80" s="4" t="inlineStr"/>
-      <c r="M80" s="4" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="n">
+        <v>0.390838</v>
+      </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI04VEA066NWDB</t>
@@ -6342,20 +6468,26 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr"/>
       <c r="J82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="4" t="inlineStr"/>
-      <c r="L82" s="4" t="inlineStr"/>
-      <c r="M82" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="n">
+        <v>92.47150000000001</v>
+      </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI06VEA156NWDB</t>
@@ -6652,20 +6784,26 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr"/>
       <c r="J86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="4" t="inlineStr"/>
-      <c r="L86" s="4" t="inlineStr"/>
-      <c r="M86" s="4" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>1995-01-01</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="n">
+        <v>2.534804</v>
+      </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI10VEA156NWDB</t>
@@ -6883,20 +7021,26 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr"/>
       <c r="J89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="4" t="inlineStr"/>
-      <c r="L89" s="4" t="inlineStr"/>
-      <c r="M89" s="4" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>1995-01-01</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>27</v>
+      </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI13VEA156NWDB</t>
@@ -7029,20 +7173,26 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr"/>
       <c r="J91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="4" t="inlineStr"/>
-      <c r="L91" s="4" t="inlineStr"/>
-      <c r="M91" s="4" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="n">
+        <v>1.231569</v>
+      </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOM01VEA644NWDB</t>
@@ -7181,20 +7331,26 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr"/>
       <c r="J93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="4" t="inlineStr"/>
-      <c r="L93" s="4" t="inlineStr"/>
-      <c r="M93" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="n">
+        <v>0.83999997</v>
+      </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI02VEA156NWDB</t>
@@ -7254,20 +7410,26 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr"/>
       <c r="J94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="4" t="inlineStr"/>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="n">
+        <v>10.5</v>
+      </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI03VEA156NWDB</t>
@@ -7327,20 +7489,26 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="4" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="n">
+        <v>63.24106999999999</v>
+      </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI04VEA156NWDB</t>
@@ -7546,20 +7714,26 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr"/>
       <c r="J98" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="4" t="inlineStr"/>
-      <c r="M98" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="n">
+        <v>604.0700099999999</v>
+      </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI07VEA156NWDB</t>
@@ -7845,7 +8019,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="n">
-        <v>6702</v>
+        <v>6707</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -7854,11 +8028,11 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>864.3948</v>
+        <v>873.4614</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
@@ -8150,20 +8324,26 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr"/>
       <c r="J106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="4" t="inlineStr"/>
-      <c r="L106" s="4" t="inlineStr"/>
-      <c r="M106" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M106" s="5" t="n">
+        <v>3042</v>
+      </c>
       <c r="N106" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FLVENA475SCEN</t>
@@ -8223,20 +8403,26 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="4" t="inlineStr"/>
-      <c r="L107" s="4" t="inlineStr"/>
-      <c r="M107" s="4" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="n">
+        <v>-3</v>
+      </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTAGCYNET32719</t>
@@ -8296,20 +8482,26 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I108" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr"/>
       <c r="J108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="4" t="inlineStr"/>
-      <c r="L108" s="4" t="inlineStr"/>
-      <c r="M108" s="4" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="n">
+        <v>88</v>
+      </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTAGCYPOS32719</t>
@@ -8369,20 +8561,26 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="5" t="n">
+        <v>499</v>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K109" s="4" t="inlineStr"/>
-      <c r="L109" s="4" t="inlineStr"/>
-      <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTAGCYVALCHG32719</t>
@@ -8442,20 +8640,26 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr"/>
       <c r="J110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="4" t="inlineStr"/>
-      <c r="L110" s="4" t="inlineStr"/>
-      <c r="M110" s="4" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="N110" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTCORPNET32719</t>
@@ -8515,20 +8719,26 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr"/>
       <c r="J111" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="4" t="inlineStr"/>
-      <c r="L111" s="4" t="inlineStr"/>
-      <c r="M111" s="4" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="n">
+        <v>1669</v>
+      </c>
       <c r="N111" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTCORPPOS32719</t>
@@ -8588,20 +8798,26 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I112" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr"/>
       <c r="J112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="4" t="inlineStr"/>
-      <c r="L112" s="4" t="inlineStr"/>
-      <c r="M112" s="4" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="n">
+        <v>-24</v>
+      </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTCORPVALCHG32719</t>
@@ -8661,20 +8877,26 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr"/>
       <c r="J113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="4" t="inlineStr"/>
-      <c r="L113" s="4" t="inlineStr"/>
-      <c r="M113" s="4" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="n">
+        <v>37</v>
+      </c>
       <c r="N113" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTEQTYNET32719</t>
@@ -8813,20 +9035,26 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr"/>
       <c r="J115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="4" t="inlineStr"/>
-      <c r="L115" s="4" t="inlineStr"/>
-      <c r="M115" s="4" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="n">
+        <v>-36</v>
+      </c>
       <c r="N115" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTEQTYVALCHG32719</t>
@@ -8886,20 +9114,26 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr"/>
       <c r="J116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="4" t="inlineStr"/>
-      <c r="L116" s="4" t="inlineStr"/>
-      <c r="M116" s="4" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="n">
+        <v>68</v>
+      </c>
       <c r="N116" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTOTALNET32719</t>
@@ -8959,20 +9193,26 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr"/>
       <c r="J117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="4" t="inlineStr"/>
-      <c r="L117" s="4" t="inlineStr"/>
-      <c r="M117" s="4" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M117" s="5" t="n">
+        <v>6044</v>
+      </c>
       <c r="N117" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTOTALPOS32719</t>
@@ -9032,20 +9272,26 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I118" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr"/>
       <c r="J118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="4" t="inlineStr"/>
-      <c r="M118" s="4" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M118" s="5" t="n">
+        <v>-61</v>
+      </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTOTALVALCHG32719</t>
@@ -9105,20 +9351,26 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr"/>
       <c r="J119" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="4" t="inlineStr"/>
-      <c r="L119" s="4" t="inlineStr"/>
-      <c r="M119" s="4" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M119" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="N119" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTREASNET32719</t>
@@ -9251,20 +9503,26 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="4" t="inlineStr"/>
-      <c r="M121" s="4" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M121" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTREASVALCHG32719</t>
@@ -9403,20 +9661,26 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr"/>
       <c r="J123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="4" t="inlineStr"/>
-      <c r="M123" s="4" t="n"/>
+        <v>282</v>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>2003-02-01</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="n">
+        <v>304</v>
+      </c>
       <c r="N123" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORSTTREASPOS32719</t>
@@ -10096,20 +10360,26 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I132" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="4" t="inlineStr"/>
-      <c r="M132" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="n">
+        <v>72907</v>
+      </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/HIVENA052SCEN</t>
@@ -10242,20 +10512,26 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I134" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr"/>
       <c r="J134" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="4" t="inlineStr"/>
-      <c r="M134" s="4" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M134" s="5" t="n">
+        <v>1125646</v>
+      </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IAVENA052SCEN</t>
@@ -10315,20 +10591,26 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr"/>
       <c r="J135" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="4" t="inlineStr"/>
-      <c r="L135" s="4" t="inlineStr"/>
-      <c r="M135" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IAVENA475SCEN</t>
@@ -10388,20 +10670,26 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I136" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr"/>
       <c r="J136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="4" t="inlineStr"/>
-      <c r="M136" s="4" t="n"/>
+        <v>71</v>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="M136" s="6" t="n">
+        <v>0.65</v>
+      </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IBANAINIAIVE</t>
@@ -10607,20 +10895,26 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr"/>
       <c r="J139" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="4" t="inlineStr"/>
-      <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="4" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>2011-10-01</t>
+        </is>
+      </c>
+      <c r="M139" s="6" t="n">
+        <v>7.7885</v>
+      </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IBANRIAIVE</t>
@@ -10753,20 +11047,26 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" s="4" t="inlineStr"/>
-      <c r="L141" s="4" t="inlineStr"/>
-      <c r="M141" s="4" t="n"/>
+        <v>123</v>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M141" s="6" t="n">
+        <v>-1.126</v>
+      </c>
       <c r="N141" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IBANRINIVE</t>
@@ -10826,20 +11126,26 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr"/>
       <c r="J142" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" s="4" t="inlineStr"/>
-      <c r="L142" s="4" t="inlineStr"/>
-      <c r="M142" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="n">
+        <v>188</v>
+      </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ICBUSEASEXQVEN</t>
@@ -10978,20 +11284,26 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr"/>
       <c r="J144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" s="4" t="inlineStr"/>
-      <c r="L144" s="4" t="inlineStr"/>
-      <c r="M144" s="4" t="n"/>
+        <v>86</v>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>1993-07-01</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="M144" s="6" t="n">
+        <v>0.1</v>
+      </c>
       <c r="N144" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDS1MNIAOFCVE</t>
@@ -11124,20 +11436,26 @@
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr"/>
       <c r="J146" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="4" t="inlineStr"/>
-      <c r="M146" s="4" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>1993-07-01</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="M146" s="6" t="n">
+        <v>1.3</v>
+      </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDS1MNIAONCVE</t>
@@ -11422,20 +11740,26 @@
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I150" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr"/>
       <c r="J150" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K150" s="4" t="inlineStr"/>
-      <c r="L150" s="4" t="inlineStr"/>
-      <c r="M150" s="4" t="n"/>
       <c r="N150" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDS1YMAORINCVE</t>
@@ -11720,20 +12044,26 @@
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I154" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr"/>
       <c r="J154" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" s="4" t="inlineStr"/>
-      <c r="L154" s="4" t="inlineStr"/>
-      <c r="M154" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>1993-10-01</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>1994-04-01</t>
+        </is>
+      </c>
+      <c r="M154" s="6" t="n">
+        <v>-0.006</v>
+      </c>
       <c r="N154" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSBMRINIVE</t>
@@ -11872,20 +12202,26 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr"/>
       <c r="J156" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" s="4" t="inlineStr"/>
-      <c r="L156" s="4" t="inlineStr"/>
-      <c r="M156" s="4" t="n"/>
+        <v>150</v>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M156" s="5" t="n">
+        <v>2397</v>
+      </c>
       <c r="N156" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMNINIVE</t>
@@ -11945,20 +12281,26 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr"/>
       <c r="J157" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" s="4" t="inlineStr"/>
-      <c r="L157" s="4" t="inlineStr"/>
-      <c r="M157" s="4" t="n"/>
+        <v>214</v>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M157" s="5" t="n">
+        <v>15950</v>
+      </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMRIAOVE</t>
@@ -12243,20 +12585,26 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I161" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr"/>
       <c r="J161" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="4" t="inlineStr"/>
-      <c r="M161" s="4" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>1987-01-01</t>
+        </is>
+      </c>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="M161" s="6" t="n">
+        <v>0.74852</v>
+      </c>
       <c r="N161" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGFCAMNIAOVE</t>
@@ -12316,20 +12664,26 @@
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr"/>
       <c r="J162" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" s="4" t="inlineStr"/>
-      <c r="L162" s="4" t="inlineStr"/>
-      <c r="M162" s="4" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>1987-04-01</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>2014-10-01</t>
+        </is>
+      </c>
+      <c r="M162" s="6" t="n">
+        <v>-0.08400000000000001</v>
+      </c>
       <c r="N162" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGFCAMNINIVE</t>
@@ -12389,20 +12743,26 @@
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr"/>
       <c r="J163" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="4" t="inlineStr"/>
-      <c r="M163" s="4" t="n"/>
+        <v>88</v>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>1993-07-01</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="M163" s="6" t="n">
+        <v>32.0498</v>
+      </c>
       <c r="N163" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGGGAMNIAOVE</t>
@@ -12462,20 +12822,26 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr"/>
       <c r="J164" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" s="4" t="inlineStr"/>
-      <c r="L164" s="4" t="inlineStr"/>
-      <c r="M164" s="4" t="n"/>
+        <v>63</v>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>1993-07-01</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M164" s="6" t="n">
+        <v>-1.12602</v>
+      </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGGGAMNINIVE</t>
@@ -12687,20 +13053,26 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I167" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr"/>
       <c r="J167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" s="4" t="inlineStr"/>
-      <c r="L167" s="4" t="inlineStr"/>
-      <c r="M167" s="4" t="n"/>
+        <v>203</v>
+      </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M167" s="5" t="n">
+        <v>4500</v>
+      </c>
       <c r="N167" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSNFAMRIAOVE</t>
@@ -12833,20 +13205,26 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I169" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr"/>
       <c r="J169" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" s="4" t="inlineStr"/>
-      <c r="L169" s="4" t="inlineStr"/>
-      <c r="M169" s="4" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>1987-01-01</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="M169" s="6" t="n">
+        <v>0.64852</v>
+      </c>
       <c r="N169" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSOFAMRIAOVE</t>
@@ -12979,20 +13357,26 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I171" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr"/>
       <c r="J171" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" s="4" t="inlineStr"/>
-      <c r="L171" s="4" t="inlineStr"/>
-      <c r="M171" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M171" s="5" t="n">
+        <v>13776</v>
+      </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDVENA052SCEN</t>
@@ -13052,20 +13436,26 @@
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I172" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr"/>
       <c r="J172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" s="4" t="inlineStr"/>
-      <c r="L172" s="4" t="inlineStr"/>
-      <c r="M172" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M172" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N172" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDVENA475SCEN</t>
@@ -13271,20 +13661,26 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr"/>
       <c r="J175" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" s="4" t="inlineStr"/>
-      <c r="L175" s="4" t="inlineStr"/>
-      <c r="M175" s="4" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>1990-10-01</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>1997-04-01</t>
+        </is>
+      </c>
+      <c r="M175" s="6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N175" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIAOVE</t>
@@ -13344,20 +13740,26 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr"/>
       <c r="J176" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" s="4" t="inlineStr"/>
-      <c r="L176" s="4" t="inlineStr"/>
-      <c r="M176" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>1993-10-01</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="M176" s="6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N176" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIGIVE</t>
@@ -13417,20 +13819,26 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr"/>
       <c r="J177" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K177" s="4" t="inlineStr"/>
-      <c r="L177" s="4" t="inlineStr"/>
-      <c r="M177" s="4" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>1993-10-01</t>
+        </is>
+      </c>
+      <c r="L177" s="4" t="inlineStr">
+        <is>
+          <t>1997-07-01</t>
+        </is>
+      </c>
+      <c r="M177" s="6" t="n">
+        <v>-0.015</v>
+      </c>
       <c r="N177" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAINIVE</t>
@@ -13490,20 +13898,26 @@
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr"/>
       <c r="J178" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" s="4" t="inlineStr"/>
-      <c r="L178" s="4" t="inlineStr"/>
-      <c r="M178" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>1990-10-01</t>
+        </is>
+      </c>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>1997-04-01</t>
+        </is>
+      </c>
+      <c r="M178" s="6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N178" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMIRIAOVE</t>
@@ -13563,20 +13977,26 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I179" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr"/>
       <c r="J179" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K179" s="4" t="inlineStr"/>
-      <c r="L179" s="4" t="inlineStr"/>
-      <c r="M179" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>1993-10-01</t>
+        </is>
+      </c>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="M179" s="6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N179" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMIRIGIVE</t>
@@ -13861,20 +14281,26 @@
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I183" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr"/>
       <c r="J183" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" s="4" t="inlineStr"/>
-      <c r="L183" s="4" t="inlineStr"/>
-      <c r="M183" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L183" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M183" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="N183" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/INVENA475SCEN</t>
@@ -14013,20 +14439,26 @@
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I185" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr"/>
       <c r="J185" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K185" s="4" t="inlineStr"/>
-      <c r="L185" s="4" t="inlineStr"/>
-      <c r="M185" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="L185" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="M185" s="6" t="n">
+        <v>246.677206628298</v>
+      </c>
       <c r="N185" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ITNETSECRP6VEN</t>
@@ -14402,20 +14834,26 @@
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I190" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="inlineStr"/>
       <c r="J190" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K190" s="4" t="inlineStr"/>
-      <c r="L190" s="4" t="inlineStr"/>
-      <c r="M190" s="4" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L190" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M190" s="5" t="n">
+        <v>1119525</v>
+      </c>
       <c r="N190" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KSVENA052SCEN</t>
@@ -14475,20 +14913,26 @@
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I191" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="inlineStr"/>
       <c r="J191" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K191" s="4" t="inlineStr"/>
-      <c r="L191" s="4" t="inlineStr"/>
-      <c r="M191" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M191" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="N191" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KSVENA475SCEN</t>
@@ -14621,20 +15065,26 @@
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I193" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr"/>
       <c r="J193" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" s="4" t="inlineStr"/>
-      <c r="L193" s="4" t="inlineStr"/>
-      <c r="M193" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M193" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="N193" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KYVENA475SCEN</t>
@@ -14773,20 +15223,26 @@
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I195" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="inlineStr"/>
       <c r="J195" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K195" s="4" t="inlineStr"/>
-      <c r="L195" s="4" t="inlineStr"/>
-      <c r="M195" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L195" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M195" s="5" t="n">
+        <v>208764595</v>
+      </c>
       <c r="N195" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/LAVENA052SCEN</t>
@@ -14846,20 +15302,26 @@
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I196" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr"/>
       <c r="J196" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" s="4" t="inlineStr"/>
-      <c r="L196" s="4" t="inlineStr"/>
-      <c r="M196" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L196" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M196" s="5" t="n">
+        <v>30</v>
+      </c>
       <c r="N196" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/LAVENA475SCEN</t>
@@ -14919,20 +15381,26 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr"/>
       <c r="J197" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" s="4" t="inlineStr"/>
-      <c r="L197" s="4" t="inlineStr"/>
-      <c r="M197" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L197" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M197" s="5" t="n">
+        <v>1854340</v>
+      </c>
       <c r="N197" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MAVENA052SCEN</t>
@@ -14992,20 +15460,26 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr"/>
       <c r="J198" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" s="4" t="inlineStr"/>
-      <c r="L198" s="4" t="inlineStr"/>
-      <c r="M198" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L198" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M198" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="N198" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MAVENA475SCEN</t>
@@ -15138,20 +15612,26 @@
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I200" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr"/>
       <c r="J200" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" s="4" t="inlineStr"/>
-      <c r="L200" s="4" t="inlineStr"/>
-      <c r="M200" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L200" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M200" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="N200" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MDVENA475SCEN</t>
@@ -15211,20 +15691,26 @@
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I201" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr"/>
       <c r="J201" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" s="4" t="inlineStr"/>
-      <c r="L201" s="4" t="inlineStr"/>
-      <c r="M201" s="4" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L201" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M201" s="5" t="n">
+        <v>419576</v>
+      </c>
       <c r="N201" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MEVENA052SCEN</t>
@@ -15284,20 +15770,26 @@
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I202" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="inlineStr"/>
       <c r="J202" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K202" s="4" t="inlineStr"/>
-      <c r="L202" s="4" t="inlineStr"/>
-      <c r="M202" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K202" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L202" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M202" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="N202" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MEVENA475SCEN</t>
@@ -15357,20 +15849,26 @@
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I203" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr"/>
       <c r="J203" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K203" s="4" t="inlineStr"/>
-      <c r="L203" s="4" t="inlineStr"/>
-      <c r="M203" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L203" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M203" s="5" t="n">
+        <v>13590192</v>
+      </c>
       <c r="N203" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MIVENA052SCEN</t>
@@ -15430,20 +15928,26 @@
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I204" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr"/>
       <c r="J204" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" s="4" t="inlineStr"/>
-      <c r="L204" s="4" t="inlineStr"/>
-      <c r="M204" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L204" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M204" s="5" t="n">
+        <v>30</v>
+      </c>
       <c r="N204" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MIVENA475SCEN</t>
@@ -15661,20 +16165,26 @@
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I207" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr"/>
       <c r="J207" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" s="4" t="inlineStr"/>
-      <c r="L207" s="4" t="inlineStr"/>
-      <c r="M207" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L207" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M207" s="5" t="n">
+        <v>1571015</v>
+      </c>
       <c r="N207" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MNVENA052SCEN</t>
@@ -15807,20 +16317,26 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I209" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr"/>
       <c r="J209" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" s="4" t="inlineStr"/>
-      <c r="L209" s="4" t="inlineStr"/>
-      <c r="M209" s="4" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L209" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M209" s="5" t="n">
+        <v>758051</v>
+      </c>
       <c r="N209" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MOVENA052SCEN</t>
@@ -15880,20 +16396,26 @@
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr"/>
       <c r="J210" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" s="4" t="inlineStr"/>
-      <c r="L210" s="4" t="inlineStr"/>
-      <c r="M210" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L210" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M210" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="N210" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MOVENA475SCEN</t>
@@ -16026,20 +16548,26 @@
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I212" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr"/>
       <c r="J212" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" s="4" t="inlineStr"/>
-      <c r="L212" s="4" t="inlineStr"/>
-      <c r="M212" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L212" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M212" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="N212" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MSVENA475SCEN</t>
@@ -16099,20 +16627,26 @@
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I213" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr"/>
       <c r="J213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" s="4" t="inlineStr"/>
-      <c r="L213" s="4" t="inlineStr"/>
-      <c r="M213" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L213" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M213" s="5" t="n">
+        <v>206865</v>
+      </c>
       <c r="N213" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA052SCEN</t>
@@ -16172,20 +16706,26 @@
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I214" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr"/>
       <c r="J214" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" s="4" t="inlineStr"/>
-      <c r="L214" s="4" t="inlineStr"/>
-      <c r="M214" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L214" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M214" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N214" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA475SCEN</t>
@@ -16324,20 +16864,26 @@
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I216" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr"/>
       <c r="J216" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" s="4" t="inlineStr"/>
-      <c r="L216" s="4" t="inlineStr"/>
-      <c r="M216" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L216" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M216" s="5" t="n">
+        <v>4804633</v>
+      </c>
       <c r="N216" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NCVENA052SCEN</t>
@@ -16397,20 +16943,26 @@
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I217" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr"/>
       <c r="J217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" s="4" t="inlineStr"/>
-      <c r="L217" s="4" t="inlineStr"/>
-      <c r="M217" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L217" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M217" s="5" t="n">
+        <v>41</v>
+      </c>
       <c r="N217" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NCVENA475SCEN</t>
@@ -16689,20 +17241,26 @@
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I221" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr"/>
       <c r="J221" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" s="4" t="inlineStr"/>
-      <c r="L221" s="4" t="inlineStr"/>
-      <c r="M221" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K221" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L221" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M221" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="N221" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NEVENA475SCEN</t>
@@ -16762,20 +17320,26 @@
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I222" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr"/>
       <c r="J222" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" s="4" t="inlineStr"/>
-      <c r="L222" s="4" t="inlineStr"/>
-      <c r="M222" s="4" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="K222" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L222" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M222" s="5" t="n">
+        <v>153807</v>
+      </c>
       <c r="N222" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NHVENA052SCEN</t>
@@ -16908,20 +17472,26 @@
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I224" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr"/>
       <c r="J224" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" s="4" t="inlineStr"/>
-      <c r="L224" s="4" t="inlineStr"/>
-      <c r="M224" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L224" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M224" s="5" t="n">
+        <v>3888969</v>
+      </c>
       <c r="N224" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NJVENA052SCEN</t>
@@ -16981,20 +17551,26 @@
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I225" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr"/>
       <c r="J225" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K225" s="4" t="inlineStr"/>
-      <c r="L225" s="4" t="inlineStr"/>
-      <c r="M225" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K225" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L225" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M225" s="5" t="n">
+        <v>53</v>
+      </c>
       <c r="N225" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NJVENA475SCEN</t>
@@ -17054,20 +17630,26 @@
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I226" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr"/>
       <c r="J226" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K226" s="4" t="inlineStr"/>
-      <c r="L226" s="4" t="inlineStr"/>
-      <c r="M226" s="4" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="K226" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L226" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M226" s="5" t="n">
+        <v>743939</v>
+      </c>
       <c r="N226" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NMVENA052SCEN</t>
@@ -17127,20 +17709,26 @@
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I227" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr"/>
       <c r="J227" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K227" s="4" t="inlineStr"/>
-      <c r="L227" s="4" t="inlineStr"/>
-      <c r="M227" s="4" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L227" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M227" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="N227" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NMVENA475SCEN</t>
@@ -17200,20 +17788,26 @@
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr"/>
       <c r="J228" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K228" s="4" t="inlineStr"/>
-      <c r="L228" s="4" t="inlineStr"/>
-      <c r="M228" s="4" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L228" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M228" s="5" t="n">
+        <v>144707</v>
+      </c>
       <c r="N228" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NVVENA052SCEN</t>
@@ -17644,20 +18238,26 @@
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I234" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr"/>
       <c r="J234" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K234" s="4" t="inlineStr"/>
-      <c r="L234" s="4" t="inlineStr"/>
-      <c r="M234" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L234" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M234" s="5" t="n">
+        <v>43</v>
+      </c>
       <c r="N234" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OHVENA475SCEN</t>
@@ -17717,20 +18317,26 @@
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I235" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="inlineStr"/>
       <c r="J235" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K235" s="4" t="inlineStr"/>
-      <c r="L235" s="4" t="inlineStr"/>
-      <c r="M235" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K235" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L235" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>111692</v>
+      </c>
       <c r="N235" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OKVENA052SCEN</t>
@@ -17790,20 +18396,26 @@
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I236" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I236" s="4" t="inlineStr"/>
       <c r="J236" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K236" s="4" t="inlineStr"/>
-      <c r="L236" s="4" t="inlineStr"/>
-      <c r="M236" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K236" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L236" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M236" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="N236" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OKVENA475SCEN</t>
@@ -17863,20 +18475,26 @@
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I237" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr"/>
       <c r="J237" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K237" s="4" t="inlineStr"/>
-      <c r="L237" s="4" t="inlineStr"/>
-      <c r="M237" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K237" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L237" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M237" s="6" t="n">
+        <v>45.86565346</v>
+      </c>
       <c r="N237" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OPENCPVEA156NUPN</t>
@@ -18009,20 +18627,26 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I239" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr"/>
       <c r="J239" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K239" s="4" t="inlineStr"/>
-      <c r="L239" s="4" t="inlineStr"/>
-      <c r="M239" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L239" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>197417</v>
+      </c>
       <c r="N239" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ORVENA052SCEN</t>
@@ -18155,20 +18779,26 @@
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I241" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I241" s="4" t="inlineStr"/>
       <c r="J241" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K241" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L241" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M241" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K241" s="4" t="inlineStr"/>
-      <c r="L241" s="4" t="inlineStr"/>
-      <c r="M241" s="4" t="n"/>
       <c r="N241" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEDESIGN</t>
@@ -18228,20 +18858,26 @@
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I242" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="inlineStr"/>
       <c r="J242" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K242" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L242" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M242" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K242" s="4" t="inlineStr"/>
-      <c r="L242" s="4" t="inlineStr"/>
-      <c r="M242" s="4" t="n"/>
       <c r="N242" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEPLANT</t>
@@ -18453,20 +19089,26 @@
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I245" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr"/>
       <c r="J245" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K245" s="4" t="inlineStr"/>
-      <c r="L245" s="4" t="inlineStr"/>
-      <c r="M245" s="4" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L245" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M245" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N245" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEUTILITY</t>
@@ -18599,20 +19241,26 @@
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I247" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr"/>
       <c r="J247" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K247" s="4" t="inlineStr"/>
-      <c r="L247" s="4" t="inlineStr"/>
-      <c r="M247" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K247" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L247" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M247" s="5" t="n">
+        <v>38</v>
+      </c>
       <c r="N247" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PAVENA475SCEN</t>
@@ -18672,20 +19320,26 @@
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I248" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr"/>
       <c r="J248" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K248" s="4" t="inlineStr"/>
-      <c r="L248" s="4" t="inlineStr"/>
-      <c r="M248" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L248" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M248" s="6" t="n">
+        <v>11809.94057</v>
+      </c>
       <c r="N248" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PC2GDPVEA620NUPN</t>
@@ -18824,20 +19478,26 @@
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I250" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr"/>
       <c r="J250" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K250" s="4" t="inlineStr"/>
-      <c r="L250" s="4" t="inlineStr"/>
-      <c r="M250" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K250" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L250" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M250" s="6" t="n">
+        <v>10445.85073</v>
+      </c>
       <c r="N250" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PCDGDPVEA620NUPN</t>
@@ -19371,20 +20031,26 @@
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I257" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr"/>
       <c r="J257" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K257" s="4" t="inlineStr"/>
-      <c r="L257" s="4" t="inlineStr"/>
-      <c r="M257" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K257" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L257" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M257" s="6" t="n">
+        <v>31.6201782226563</v>
+      </c>
       <c r="N257" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLGDPOVEA670NRUG</t>
@@ -19444,20 +20110,26 @@
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I258" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr"/>
       <c r="J258" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K258" s="4" t="inlineStr"/>
-      <c r="L258" s="4" t="inlineStr"/>
-      <c r="M258" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L258" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M258" s="6" t="n">
+        <v>40.4344416781944</v>
+      </c>
       <c r="N258" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLICPPVEA670NRUG</t>
@@ -19675,20 +20347,26 @@
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I261" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr"/>
       <c r="J261" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K261" s="4" t="inlineStr"/>
-      <c r="L261" s="4" t="inlineStr"/>
-      <c r="M261" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L261" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M261" s="6" t="n">
+        <v>121.4234463</v>
+      </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOCONVEA622NUPN</t>
@@ -19827,20 +20505,26 @@
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I263" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr"/>
       <c r="J263" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K263" s="4" t="inlineStr"/>
-      <c r="L263" s="4" t="inlineStr"/>
-      <c r="M263" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L263" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M263" s="6" t="n">
+        <v>144.0149859</v>
+      </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOGINVEA623NUPN</t>
@@ -20370,20 +21054,26 @@
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I270" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr"/>
       <c r="J270" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K270" s="4" t="inlineStr"/>
-      <c r="L270" s="4" t="inlineStr"/>
-      <c r="M270" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L270" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M270" s="6" t="n">
+        <v>320634.9337</v>
+      </c>
       <c r="N270" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PPPGDPVEA619NUPN</t>
@@ -20601,20 +21291,26 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I273" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr"/>
       <c r="J273" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K273" s="4" t="inlineStr"/>
-      <c r="L273" s="4" t="inlineStr"/>
-      <c r="M273" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K273" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L273" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M273" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="N273" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PRVENA475SCEN</t>
@@ -21385,20 +22081,26 @@
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I283" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr"/>
       <c r="J283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K283" s="4" t="inlineStr"/>
-      <c r="L283" s="4" t="inlineStr"/>
-      <c r="M283" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L283" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M283" s="6" t="n">
+        <v>25811.10218</v>
+      </c>
       <c r="N283" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPTEVEA629NUPN</t>
@@ -21537,20 +22239,26 @@
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I285" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I285" s="4" t="inlineStr"/>
       <c r="J285" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K285" s="4" t="inlineStr"/>
-      <c r="L285" s="4" t="inlineStr"/>
-      <c r="M285" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K285" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L285" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M285" s="6" t="n">
+        <v>10406.06094</v>
+      </c>
       <c r="N285" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPTTVEA625NUPN</t>
@@ -21610,20 +22318,26 @@
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I286" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr"/>
       <c r="J286" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K286" s="4" t="inlineStr"/>
-      <c r="L286" s="4" t="inlineStr"/>
-      <c r="M286" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K286" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L286" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M286" s="6" t="n">
+        <v>19511.40489</v>
+      </c>
       <c r="N286" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPWOVEA627NUPN</t>
@@ -21683,20 +22397,26 @@
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I287" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I287" s="4" t="inlineStr"/>
       <c r="J287" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K287" s="4" t="inlineStr"/>
-      <c r="L287" s="4" t="inlineStr"/>
-      <c r="M287" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K287" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L287" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M287" s="5" t="n">
+        <v>281736</v>
+      </c>
       <c r="N287" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RIVENA052SCEN</t>
@@ -21756,20 +22476,26 @@
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I288" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I288" s="4" t="inlineStr"/>
       <c r="J288" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K288" s="4" t="inlineStr"/>
-      <c r="L288" s="4" t="inlineStr"/>
-      <c r="M288" s="4" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="K288" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L288" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M288" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N288" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RIVENA475SCEN</t>
@@ -21987,20 +22713,26 @@
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I291" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I291" s="4" t="inlineStr"/>
       <c r="J291" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K291" s="4" t="inlineStr"/>
-      <c r="L291" s="4" t="inlineStr"/>
-      <c r="M291" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K291" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L291" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M291" s="5" t="n">
+        <v>15077425</v>
+      </c>
       <c r="N291" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SCVENA052SCEN</t>
@@ -22060,20 +22792,26 @@
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I292" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I292" s="4" t="inlineStr"/>
       <c r="J292" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K292" s="4" t="inlineStr"/>
-      <c r="L292" s="4" t="inlineStr"/>
-      <c r="M292" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K292" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L292" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M292" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="N292" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SCVENA475SCEN</t>
@@ -22206,20 +22944,26 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I294" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I294" s="4" t="inlineStr"/>
       <c r="J294" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K294" s="4" t="inlineStr"/>
-      <c r="L294" s="4" t="inlineStr"/>
-      <c r="M294" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K294" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L294" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M294" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="N294" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SDVENA475SCEN</t>
@@ -22431,20 +23175,26 @@
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I297" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I297" s="4" t="inlineStr"/>
       <c r="J297" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K297" s="4" t="inlineStr"/>
-      <c r="L297" s="4" t="inlineStr"/>
-      <c r="M297" s="4" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="K297" s="4" t="inlineStr">
+        <is>
+          <t>1971-01-01</t>
+        </is>
+      </c>
+      <c r="L297" s="4" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M297" s="6" t="n">
+        <v>1.0806200504303</v>
+      </c>
       <c r="N297" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRSECOFMZSVEN</t>
@@ -22504,20 +23254,26 @@
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I298" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr"/>
       <c r="J298" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K298" s="4" t="inlineStr"/>
-      <c r="L298" s="4" t="inlineStr"/>
-      <c r="M298" s="4" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="K298" s="4" t="inlineStr">
+        <is>
+          <t>1986-01-01</t>
+        </is>
+      </c>
+      <c r="L298" s="4" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="M298" s="6" t="n">
+        <v>1.40991997718811</v>
+      </c>
       <c r="N298" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRTERTFMZSVEN</t>
@@ -22972,20 +23728,26 @@
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I304" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I304" s="4" t="inlineStr"/>
       <c r="J304" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K304" s="4" t="inlineStr"/>
-      <c r="L304" s="4" t="inlineStr"/>
-      <c r="M304" s="4" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="K304" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L304" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M304" s="5" t="n">
+        <v>1404448</v>
+      </c>
       <c r="N304" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SMPOPTOTLVEN</t>
@@ -23440,20 +24202,26 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I310" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I310" s="4" t="inlineStr"/>
       <c r="J310" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K310" s="4" t="inlineStr"/>
-      <c r="L310" s="4" t="inlineStr"/>
-      <c r="M310" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="K310" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L310" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M310" s="6" t="n">
+        <v>24.9159954154898</v>
+      </c>
       <c r="N310" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPPOP0014TOZSVEN</t>
@@ -23969,20 +24737,26 @@
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I317" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I317" s="4" t="inlineStr"/>
       <c r="J317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K317" s="4" t="inlineStr"/>
-      <c r="L317" s="4" t="inlineStr"/>
-      <c r="M317" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K317" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L317" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M317" s="5" t="n">
+        <v>297118823</v>
+      </c>
       <c r="N317" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/TXVENA052SCEN</t>
@@ -24042,20 +24816,26 @@
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I318" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I318" s="4" t="inlineStr"/>
       <c r="J318" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K318" s="4" t="inlineStr"/>
-      <c r="L318" s="4" t="inlineStr"/>
-      <c r="M318" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K318" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L318" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M318" s="5" t="n">
+        <v>169</v>
+      </c>
       <c r="N318" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/TXVENA475SCEN</t>
@@ -24115,20 +24895,26 @@
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I319" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I319" s="4" t="inlineStr"/>
       <c r="J319" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="K319" s="4" t="inlineStr">
+        <is>
+          <t>1994-04-01</t>
+        </is>
+      </c>
+      <c r="L319" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M319" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K319" s="4" t="inlineStr"/>
-      <c r="L319" s="4" t="inlineStr"/>
-      <c r="M319" s="4" t="n"/>
       <c r="N319" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTBONDNET32719</t>
@@ -24188,20 +24974,26 @@
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I320" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I320" s="4" t="inlineStr"/>
       <c r="J320" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K320" s="4" t="inlineStr"/>
-      <c r="L320" s="4" t="inlineStr"/>
-      <c r="M320" s="4" t="n"/>
+        <v>389</v>
+      </c>
+      <c r="K320" s="4" t="inlineStr">
+        <is>
+          <t>1994-03-01</t>
+        </is>
+      </c>
+      <c r="L320" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M320" s="5" t="n">
+        <v>4989</v>
+      </c>
       <c r="N320" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTBONDPOS32719</t>
@@ -24261,20 +25053,26 @@
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I321" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I321" s="4" t="inlineStr"/>
       <c r="J321" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K321" s="4" t="inlineStr"/>
-      <c r="L321" s="4" t="inlineStr"/>
-      <c r="M321" s="4" t="n"/>
+        <v>388</v>
+      </c>
+      <c r="K321" s="4" t="inlineStr">
+        <is>
+          <t>1994-04-01</t>
+        </is>
+      </c>
+      <c r="L321" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M321" s="5" t="n">
+        <v>35</v>
+      </c>
       <c r="N321" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTBONDVALCHG32719</t>
@@ -24334,20 +25132,26 @@
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I322" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I322" s="4" t="inlineStr"/>
       <c r="J322" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K322" s="4" t="inlineStr"/>
-      <c r="L322" s="4" t="inlineStr"/>
-      <c r="M322" s="4" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="K322" s="4" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="L322" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M322" s="5" t="n">
+        <v>37</v>
+      </c>
       <c r="N322" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTCORPBONDNET32719</t>
@@ -24486,20 +25290,26 @@
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I324" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I324" s="4" t="inlineStr"/>
       <c r="J324" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K324" s="4" t="inlineStr"/>
-      <c r="L324" s="4" t="inlineStr"/>
-      <c r="M324" s="4" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="K324" s="4" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="L324" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M324" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N324" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTCORPBONDVALCHG32719</t>
@@ -24638,20 +25448,26 @@
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I326" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I326" s="4" t="inlineStr"/>
       <c r="J326" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K326" s="4" t="inlineStr"/>
-      <c r="L326" s="4" t="inlineStr"/>
-      <c r="M326" s="4" t="n"/>
+        <v>389</v>
+      </c>
+      <c r="K326" s="4" t="inlineStr">
+        <is>
+          <t>1994-03-01</t>
+        </is>
+      </c>
+      <c r="L326" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M326" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="N326" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTEQTYPOS32719</t>
@@ -24711,20 +25527,26 @@
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I327" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I327" s="4" t="inlineStr"/>
       <c r="J327" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="K327" s="4" t="inlineStr">
+        <is>
+          <t>1994-04-01</t>
+        </is>
+      </c>
+      <c r="L327" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M327" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K327" s="4" t="inlineStr"/>
-      <c r="L327" s="4" t="inlineStr"/>
-      <c r="M327" s="4" t="n"/>
       <c r="N327" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTEQTYVALCHG32719</t>
@@ -24784,20 +25606,26 @@
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I328" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I328" s="4" t="inlineStr"/>
       <c r="J328" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K328" s="4" t="inlineStr"/>
-      <c r="L328" s="4" t="inlineStr"/>
-      <c r="M328" s="4" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="K328" s="4" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="L328" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M328" s="5" t="n">
+        <v>-37</v>
+      </c>
       <c r="N328" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTGOVTBONDNET32719</t>
@@ -24857,20 +25685,26 @@
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I329" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I329" s="4" t="inlineStr"/>
       <c r="J329" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K329" s="4" t="inlineStr"/>
-      <c r="L329" s="4" t="inlineStr"/>
-      <c r="M329" s="4" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="K329" s="4" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="L329" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M329" s="5" t="n">
+        <v>2376</v>
+      </c>
       <c r="N329" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTGOVTBONDPOS32719</t>
@@ -24930,20 +25764,26 @@
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I330" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I330" s="4" t="inlineStr"/>
       <c r="J330" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K330" s="4" t="inlineStr"/>
-      <c r="L330" s="4" t="inlineStr"/>
-      <c r="M330" s="4" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="K330" s="4" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="L330" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M330" s="5" t="n">
+        <v>34</v>
+      </c>
       <c r="N330" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTGOVTBONDVALCHG32719</t>
@@ -25003,20 +25843,26 @@
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I331" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I331" s="4" t="inlineStr"/>
       <c r="J331" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="K331" s="4" t="inlineStr">
+        <is>
+          <t>1994-04-01</t>
+        </is>
+      </c>
+      <c r="L331" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M331" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K331" s="4" t="inlineStr"/>
-      <c r="L331" s="4" t="inlineStr"/>
-      <c r="M331" s="4" t="n"/>
       <c r="N331" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALNET32719</t>
@@ -25076,20 +25922,26 @@
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I332" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I332" s="4" t="inlineStr"/>
       <c r="J332" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K332" s="4" t="inlineStr"/>
-      <c r="L332" s="4" t="inlineStr"/>
-      <c r="M332" s="4" t="n"/>
+        <v>389</v>
+      </c>
+      <c r="K332" s="4" t="inlineStr">
+        <is>
+          <t>1994-03-01</t>
+        </is>
+      </c>
+      <c r="L332" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M332" s="5" t="n">
+        <v>4996</v>
+      </c>
       <c r="N332" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALPOS32719</t>
@@ -25149,20 +26001,26 @@
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I333" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I333" s="4" t="inlineStr"/>
       <c r="J333" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K333" s="4" t="inlineStr"/>
-      <c r="L333" s="4" t="inlineStr"/>
-      <c r="M333" s="4" t="n"/>
+        <v>388</v>
+      </c>
+      <c r="K333" s="4" t="inlineStr">
+        <is>
+          <t>1994-04-01</t>
+        </is>
+      </c>
+      <c r="L333" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M333" s="5" t="n">
+        <v>35</v>
+      </c>
       <c r="N333" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALVALCHG32719</t>
@@ -25222,20 +26080,26 @@
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I334" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I334" s="4" t="inlineStr"/>
       <c r="J334" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K334" s="4" t="inlineStr"/>
-      <c r="L334" s="4" t="inlineStr"/>
-      <c r="M334" s="4" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="K334" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L334" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M334" s="5" t="n">
+        <v>910607</v>
+      </c>
       <c r="N334" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/UTVENA052SCEN</t>
@@ -25295,20 +26159,26 @@
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I335" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I335" s="4" t="inlineStr"/>
       <c r="J335" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K335" s="4" t="inlineStr"/>
-      <c r="L335" s="4" t="inlineStr"/>
-      <c r="M335" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K335" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L335" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M335" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/UTVENA475SCEN</t>
@@ -25441,20 +26311,26 @@
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr"/>
       <c r="J337" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K337" s="4" t="inlineStr"/>
-      <c r="L337" s="4" t="inlineStr"/>
-      <c r="M337" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L337" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M337" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="N337" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VAVENA475SCEN</t>
@@ -25660,20 +26536,26 @@
       </c>
       <c r="H340" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I340" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I340" s="4" t="inlineStr"/>
       <c r="J340" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K340" s="4" t="inlineStr"/>
-      <c r="L340" s="4" t="inlineStr"/>
-      <c r="M340" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K340" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L340" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M340" s="5" t="n">
+        <v>10429</v>
+      </c>
       <c r="N340" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCACNUM</t>
@@ -25733,20 +26615,26 @@
       </c>
       <c r="H341" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I341" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I341" s="4" t="inlineStr"/>
       <c r="J341" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K341" s="4" t="inlineStr"/>
-      <c r="L341" s="4" t="inlineStr"/>
-      <c r="M341" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K341" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L341" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M341" s="6" t="n">
+        <v>11.8235927668</v>
+      </c>
       <c r="N341" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAKNUM</t>
@@ -25806,20 +26694,26 @@
       </c>
       <c r="H342" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I342" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I342" s="4" t="inlineStr"/>
       <c r="J342" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K342" s="4" t="inlineStr"/>
-      <c r="L342" s="4" t="inlineStr"/>
-      <c r="M342" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K342" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L342" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M342" s="6" t="n">
+        <v>1442.4719851783</v>
+      </c>
       <c r="N342" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODCANUM</t>
@@ -25879,20 +26773,26 @@
       </c>
       <c r="H343" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I343" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I343" s="4" t="inlineStr"/>
       <c r="J343" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K343" s="4" t="inlineStr"/>
-      <c r="L343" s="4" t="inlineStr"/>
-      <c r="M343" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K343" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L343" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M343" s="5" t="n">
+        <v>31695711</v>
+      </c>
       <c r="N343" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODCNUM</t>
@@ -25952,20 +26852,26 @@
       </c>
       <c r="H344" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I344" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I344" s="4" t="inlineStr"/>
       <c r="J344" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K344" s="4" t="inlineStr"/>
-      <c r="L344" s="4" t="inlineStr"/>
-      <c r="M344" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K344" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L344" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M344" s="5" t="n">
+        <v>21794</v>
+      </c>
       <c r="N344" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODDNUM</t>
@@ -26025,20 +26931,26 @@
       </c>
       <c r="H345" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I345" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I345" s="4" t="inlineStr"/>
       <c r="J345" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K345" s="4" t="inlineStr"/>
-      <c r="L345" s="4" t="inlineStr"/>
-      <c r="M345" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K345" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L345" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M345" s="5" t="n">
+        <v>270382</v>
+      </c>
       <c r="N345" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODMFNUM</t>
@@ -26177,20 +27089,26 @@
       </c>
       <c r="H347" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I347" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I347" s="4" t="inlineStr"/>
       <c r="J347" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K347" s="4" t="inlineStr"/>
-      <c r="L347" s="4" t="inlineStr"/>
-      <c r="M347" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K347" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L347" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M347" s="5" t="n">
+        <v>536976</v>
+      </c>
       <c r="N347" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAOFILPNUM</t>
@@ -26542,20 +27460,26 @@
       </c>
       <c r="H352" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I352" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I352" s="4" t="inlineStr"/>
       <c r="J352" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K352" s="4" t="inlineStr"/>
-      <c r="L352" s="4" t="inlineStr"/>
-      <c r="M352" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K352" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L352" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M352" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="N352" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODDLNUM</t>
@@ -26615,20 +27539,26 @@
       </c>
       <c r="H353" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I353" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I353" s="4" t="inlineStr"/>
       <c r="J353" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K353" s="4" t="inlineStr"/>
-      <c r="L353" s="4" t="inlineStr"/>
-      <c r="M353" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K353" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L353" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M353" s="5" t="n">
+        <v>32</v>
+      </c>
       <c r="N353" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODDNUM</t>
@@ -26688,20 +27618,26 @@
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I354" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I354" s="4" t="inlineStr"/>
       <c r="J354" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K354" s="4" t="inlineStr"/>
-      <c r="L354" s="4" t="inlineStr"/>
-      <c r="M354" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K354" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L354" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M354" s="6" t="n">
+        <v>0.130378096</v>
+      </c>
       <c r="N354" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODMFKNUM</t>
@@ -26761,20 +27697,26 @@
       </c>
       <c r="H355" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I355" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I355" s="4" t="inlineStr"/>
       <c r="J355" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K355" s="4" t="inlineStr"/>
-      <c r="L355" s="4" t="inlineStr"/>
-      <c r="M355" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K355" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L355" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M355" s="5" t="n">
+        <v>47</v>
+      </c>
       <c r="N355" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODMFLNUM</t>
@@ -26907,20 +27849,26 @@
       </c>
       <c r="H357" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I357" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I357" s="4" t="inlineStr"/>
       <c r="J357" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K357" s="4" t="inlineStr"/>
-      <c r="L357" s="4" t="inlineStr"/>
-      <c r="M357" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K357" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L357" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M357" s="6" t="n">
+        <v>1889.1919863706</v>
+      </c>
       <c r="N357" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCANUM</t>
@@ -26980,20 +27928,26 @@
       </c>
       <c r="H358" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I358" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I358" s="4" t="inlineStr"/>
       <c r="J358" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K358" s="4" t="inlineStr"/>
-      <c r="L358" s="4" t="inlineStr"/>
-      <c r="M358" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K358" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L358" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M358" s="6" t="n">
+        <v>1119.62371720568</v>
+      </c>
       <c r="N358" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCHANUM</t>
@@ -27053,20 +28007,26 @@
       </c>
       <c r="H359" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I359" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I359" s="4" t="inlineStr"/>
       <c r="J359" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K359" s="4" t="inlineStr"/>
-      <c r="L359" s="4" t="inlineStr"/>
-      <c r="M359" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K359" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L359" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M359" s="6" t="n">
+        <v>24601704.6666667</v>
+      </c>
       <c r="N359" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCHPENUM</t>
@@ -27126,20 +28086,26 @@
       </c>
       <c r="H360" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I360" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I360" s="4" t="inlineStr"/>
       <c r="J360" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K360" s="4" t="inlineStr"/>
-      <c r="L360" s="4" t="inlineStr"/>
-      <c r="M360" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K360" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L360" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M360" s="5" t="n">
+        <v>41472676</v>
+      </c>
       <c r="N360" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCPENUM</t>
@@ -27199,20 +28165,26 @@
       </c>
       <c r="H361" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I361" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I361" s="4" t="inlineStr"/>
       <c r="J361" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K361" s="4" t="inlineStr"/>
-      <c r="L361" s="4" t="inlineStr"/>
-      <c r="M361" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K361" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L361" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M361" s="6" t="n">
+        <v>481500.416666667</v>
+      </c>
       <c r="N361" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPENUM</t>
@@ -27272,20 +28244,26 @@
       </c>
       <c r="H362" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I362" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I362" s="4" t="inlineStr"/>
       <c r="J362" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K362" s="4" t="inlineStr"/>
-      <c r="L362" s="4" t="inlineStr"/>
-      <c r="M362" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K362" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L362" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M362" s="6" t="n">
+        <v>66.83665774000001</v>
+      </c>
       <c r="N362" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPNUM</t>
@@ -27418,20 +28396,26 @@
       </c>
       <c r="H364" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I364" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I364" s="4" t="inlineStr"/>
       <c r="J364" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K364" s="4" t="inlineStr"/>
-      <c r="L364" s="4" t="inlineStr"/>
-      <c r="M364" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K364" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L364" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M364" s="5" t="n">
+        <v>4202016</v>
+      </c>
       <c r="N364" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDOFINPPENUM</t>
@@ -27570,20 +28554,26 @@
       </c>
       <c r="H366" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I366" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I366" s="4" t="inlineStr"/>
       <c r="J366" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K366" s="4" t="inlineStr"/>
-      <c r="L366" s="4" t="inlineStr"/>
-      <c r="M366" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K366" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L366" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M366" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="N366" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIODDNUM</t>
@@ -27643,20 +28633,26 @@
       </c>
       <c r="H367" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I367" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I367" s="4" t="inlineStr"/>
       <c r="J367" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K367" s="4" t="inlineStr"/>
-      <c r="L367" s="4" t="inlineStr"/>
-      <c r="M367" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K367" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L367" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M367" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="N367" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIODMFNUM</t>
@@ -27716,20 +28712,26 @@
       </c>
       <c r="H368" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I368" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I368" s="4" t="inlineStr"/>
       <c r="J368" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K368" s="4" t="inlineStr"/>
-      <c r="L368" s="4" t="inlineStr"/>
-      <c r="M368" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K368" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L368" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M368" s="5" t="n">
+        <v>48</v>
+      </c>
       <c r="N368" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIOFINUM</t>
@@ -27789,20 +28791,26 @@
       </c>
       <c r="H369" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I369" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I369" s="4" t="inlineStr"/>
       <c r="J369" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K369" s="4" t="inlineStr"/>
-      <c r="L369" s="4" t="inlineStr"/>
-      <c r="M369" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K369" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L369" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M369" s="6" t="n">
+        <v>68.50582168130001</v>
+      </c>
       <c r="N369" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCGGDPPT</t>
@@ -27862,20 +28870,26 @@
       </c>
       <c r="H370" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I370" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I370" s="4" t="inlineStr"/>
       <c r="J370" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K370" s="4" t="inlineStr"/>
-      <c r="L370" s="4" t="inlineStr"/>
-      <c r="M370" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K370" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L370" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M370" s="6" t="n">
+        <v>23.7831197319</v>
+      </c>
       <c r="N370" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCHGGDPPT</t>
@@ -27935,20 +28949,26 @@
       </c>
       <c r="H371" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I371" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I371" s="4" t="inlineStr"/>
       <c r="J371" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K371" s="4" t="inlineStr"/>
-      <c r="L371" s="4" t="inlineStr"/>
-      <c r="M371" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K371" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L371" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M371" s="6" t="n">
+        <v>1451895895202.22</v>
+      </c>
       <c r="N371" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCHXDC</t>
@@ -28008,20 +29028,26 @@
       </c>
       <c r="H372" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I372" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I372" s="4" t="inlineStr"/>
       <c r="J372" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K372" s="4" t="inlineStr"/>
-      <c r="L372" s="4" t="inlineStr"/>
-      <c r="M372" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K372" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L372" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M372" s="6" t="n">
+        <v>21.4396202031903</v>
+      </c>
       <c r="N372" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCSGGDPPT</t>
@@ -28081,20 +29107,26 @@
       </c>
       <c r="H373" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I373" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I373" s="4" t="inlineStr"/>
       <c r="J373" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K373" s="4" t="inlineStr"/>
-      <c r="L373" s="4" t="inlineStr"/>
-      <c r="M373" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K373" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L373" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M373" s="6" t="n">
+        <v>481500416666.6671</v>
+      </c>
       <c r="N373" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCSXDC</t>
@@ -28227,20 +29259,26 @@
       </c>
       <c r="H375" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I375" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I375" s="4" t="inlineStr"/>
       <c r="J375" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K375" s="4" t="inlineStr"/>
-      <c r="L375" s="4" t="inlineStr"/>
-      <c r="M375" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="K375" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L375" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M375" s="6" t="n">
+        <v>2531710068.02</v>
+      </c>
       <c r="N375" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODDXDC</t>
@@ -28300,20 +29338,26 @@
       </c>
       <c r="H376" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I376" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I376" s="4" t="inlineStr"/>
       <c r="J376" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K376" s="4" t="inlineStr"/>
-      <c r="L376" s="4" t="inlineStr"/>
-      <c r="M376" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K376" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L376" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M376" s="6" t="n">
+        <v>37322701822.99</v>
+      </c>
       <c r="N376" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODMFXDC</t>
@@ -28373,20 +29417,26 @@
       </c>
       <c r="H377" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I377" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I377" s="4" t="inlineStr"/>
       <c r="J377" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K377" s="4" t="inlineStr"/>
-      <c r="L377" s="4" t="inlineStr"/>
-      <c r="M377" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K377" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L377" s="4" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M377" s="5" t="n">
+        <v>359000000</v>
+      </c>
       <c r="N377" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLOFILPXDC</t>
@@ -28750,20 +29800,26 @@
       </c>
       <c r="H382" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I382" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I382" s="4" t="inlineStr"/>
       <c r="J382" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K382" s="4" t="inlineStr"/>
-      <c r="L382" s="4" t="inlineStr"/>
-      <c r="M382" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K382" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L382" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M382" s="5" t="n">
+        <v>5466</v>
+      </c>
       <c r="N382" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODDNUM</t>
@@ -28823,20 +29879,26 @@
       </c>
       <c r="H383" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I383" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I383" s="4" t="inlineStr"/>
       <c r="J383" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K383" s="4" t="inlineStr"/>
-      <c r="L383" s="4" t="inlineStr"/>
-      <c r="M383" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K383" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L383" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M383" s="5" t="n">
+        <v>42341</v>
+      </c>
       <c r="N383" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODMFNUM</t>
@@ -28969,20 +30031,26 @@
       </c>
       <c r="H385" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I385" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I385" s="4" t="inlineStr"/>
       <c r="J385" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K385" s="4" t="inlineStr"/>
-      <c r="L385" s="4" t="inlineStr"/>
-      <c r="M385" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K385" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L385" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M385" s="6" t="n">
+        <v>336.987464420657</v>
+      </c>
       <c r="N385" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHANUM</t>
@@ -29042,20 +30110,26 @@
       </c>
       <c r="H386" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I386" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I386" s="4" t="inlineStr"/>
       <c r="J386" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K386" s="4" t="inlineStr"/>
-      <c r="L386" s="4" t="inlineStr"/>
-      <c r="M386" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K386" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L386" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M386" s="6" t="n">
+        <v>7404689.58333333</v>
+      </c>
       <c r="N386" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHPENUM</t>
@@ -29261,20 +30335,26 @@
       </c>
       <c r="H389" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I389" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I389" s="4" t="inlineStr"/>
       <c r="J389" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K389" s="4" t="inlineStr"/>
-      <c r="L389" s="4" t="inlineStr"/>
-      <c r="M389" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K389" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L389" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M389" s="6" t="n">
+        <v>41.2593449</v>
+      </c>
       <c r="N389" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCSPNUM</t>
@@ -29334,20 +30414,26 @@
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I390" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I390" s="4" t="inlineStr"/>
       <c r="J390" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K390" s="4" t="inlineStr"/>
-      <c r="L390" s="4" t="inlineStr"/>
-      <c r="M390" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K390" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L390" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M390" s="6" t="n">
+        <v>37.8908354029</v>
+      </c>
       <c r="N390" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCGGDPPT</t>
@@ -29559,20 +30645,26 @@
       </c>
       <c r="H393" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I393" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I393" s="4" t="inlineStr"/>
       <c r="J393" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K393" s="4" t="inlineStr"/>
-      <c r="L393" s="4" t="inlineStr"/>
-      <c r="M393" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K393" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L393" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M393" s="6" t="n">
+        <v>2437538671645.28</v>
+      </c>
       <c r="N393" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCXDC</t>
@@ -29632,20 +30724,26 @@
       </c>
       <c r="H394" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I394" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I394" s="4" t="inlineStr"/>
       <c r="J394" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K394" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L394" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M394" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K394" s="4" t="inlineStr"/>
-      <c r="L394" s="4" t="inlineStr"/>
-      <c r="M394" s="4" t="n"/>
       <c r="N394" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODDSXDC</t>
@@ -29705,20 +30803,26 @@
       </c>
       <c r="H395" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I395" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I395" s="4" t="inlineStr"/>
       <c r="J395" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K395" s="4" t="inlineStr"/>
-      <c r="L395" s="4" t="inlineStr"/>
-      <c r="M395" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="K395" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L395" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M395" s="6" t="n">
+        <v>1878132857.56</v>
+      </c>
       <c r="N395" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODDXDC</t>
@@ -29778,20 +30882,26 @@
       </c>
       <c r="H396" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I396" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I396" s="4" t="inlineStr"/>
       <c r="J396" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K396" s="4" t="inlineStr"/>
-      <c r="L396" s="4" t="inlineStr"/>
-      <c r="M396" s="4" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="K396" s="4" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="L396" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M396" s="5" t="n">
+        <v>10753000000</v>
+      </c>
       <c r="N396" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFSXDC</t>
@@ -29851,20 +30961,26 @@
       </c>
       <c r="H397" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I397" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I397" s="4" t="inlineStr"/>
       <c r="J397" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K397" s="4" t="inlineStr"/>
-      <c r="L397" s="4" t="inlineStr"/>
-      <c r="M397" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K397" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L397" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M397" s="6" t="n">
+        <v>27106310381.76</v>
+      </c>
       <c r="N397" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFXDC</t>
@@ -29924,20 +31040,26 @@
       </c>
       <c r="H398" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I398" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I398" s="4" t="inlineStr"/>
       <c r="J398" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K398" s="4" t="inlineStr"/>
-      <c r="L398" s="4" t="inlineStr"/>
-      <c r="M398" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K398" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L398" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M398" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N398" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VIVENA475SCEN</t>
@@ -29997,20 +31119,26 @@
       </c>
       <c r="H399" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I399" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I399" s="4" t="inlineStr"/>
       <c r="J399" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K399" s="4" t="inlineStr"/>
-      <c r="L399" s="4" t="inlineStr"/>
-      <c r="M399" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K399" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L399" s="4" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="M399" s="5" t="n">
+        <v>466033</v>
+      </c>
       <c r="N399" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VTVENA052SCEN</t>
@@ -30143,20 +31271,26 @@
       </c>
       <c r="H401" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I401" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I401" s="4" t="inlineStr"/>
       <c r="J401" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K401" s="4" t="inlineStr"/>
-      <c r="L401" s="4" t="inlineStr"/>
-      <c r="M401" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K401" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L401" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M401" s="5" t="n">
+        <v>2501814</v>
+      </c>
       <c r="N401" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WAVENA052SCEN</t>
@@ -30216,20 +31350,26 @@
       </c>
       <c r="H402" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I402" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I402" s="4" t="inlineStr"/>
       <c r="J402" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K402" s="4" t="inlineStr"/>
-      <c r="L402" s="4" t="inlineStr"/>
-      <c r="M402" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K402" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L402" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M402" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="N402" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WAVENA475SCEN</t>
@@ -30289,20 +31429,26 @@
       </c>
       <c r="H403" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I403" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I403" s="4" t="inlineStr"/>
       <c r="J403" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K403" s="4" t="inlineStr"/>
-      <c r="L403" s="4" t="inlineStr"/>
-      <c r="M403" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K403" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L403" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M403" s="5" t="n">
+        <v>2392941</v>
+      </c>
       <c r="N403" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WIVENA052SCEN</t>
@@ -30362,20 +31508,26 @@
       </c>
       <c r="H404" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I404" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I404" s="4" t="inlineStr"/>
       <c r="J404" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K404" s="4" t="inlineStr"/>
-      <c r="L404" s="4" t="inlineStr"/>
-      <c r="M404" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K404" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L404" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M404" s="5" t="n">
+        <v>29</v>
+      </c>
       <c r="N404" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WIVENA475SCEN</t>
@@ -30508,20 +31660,26 @@
       </c>
       <c r="H406" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I406" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I406" s="4" t="inlineStr"/>
       <c r="J406" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K406" s="4" t="inlineStr"/>
-      <c r="L406" s="4" t="inlineStr"/>
-      <c r="M406" s="4" t="n"/>
+        <v>290</v>
+      </c>
+      <c r="K406" s="4" t="inlineStr">
+        <is>
+          <t>1954-01-01</t>
+        </is>
+      </c>
+      <c r="L406" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M406" s="6" t="n">
+        <v>0.269383</v>
+      </c>
       <c r="N406" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WUIMAVEN</t>
@@ -30660,20 +31818,26 @@
       </c>
       <c r="H408" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I408" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I408" s="4" t="inlineStr"/>
       <c r="J408" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="K408" s="4" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="L408" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M408" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K408" s="4" t="inlineStr"/>
-      <c r="L408" s="4" t="inlineStr"/>
-      <c r="M408" s="4" t="n"/>
       <c r="N408" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WUPIVEN</t>
@@ -30885,20 +32049,26 @@
       </c>
       <c r="H411" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I411" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I411" s="4" t="inlineStr"/>
       <c r="J411" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K411" s="4" t="inlineStr"/>
-      <c r="L411" s="4" t="inlineStr"/>
-      <c r="M411" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="K411" s="4" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="L411" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M411" s="5" t="n">
+        <v>43832725</v>
+      </c>
       <c r="N411" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WYVENA052SCEN</t>
@@ -31152,7 +32322,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -31209,7 +32379,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>123</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15">
@@ -31219,7 +32389,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>16411</v>
+        <v>31840</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -681,26 +681,20 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>83990</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/AKVENA052SCEN</t>
@@ -833,26 +827,20 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J9" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>1063662</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ALVENA052SCEN</t>
@@ -985,26 +973,20 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J11" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>273623</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="n"/>
       <c r="N11" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ARVENA052SCEN</t>
@@ -1289,26 +1271,20 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J15" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/AZVENA475SCEN</t>
@@ -1526,26 +1502,20 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J18" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>14700660</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CAVENA052SCEN</t>
@@ -2146,26 +2116,20 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J26" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/COVENA475SCEN</t>
@@ -2225,26 +2189,20 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J27" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0.449208825826645</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHCCPVEA156NRUG</t>
@@ -2456,26 +2414,20 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J30" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>-0.301709741353989</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHMCPVEA156NRUG</t>
@@ -2535,26 +2487,20 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J31" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="n">
-        <v>-0.0894852876663208</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHRCPVEA156NRUG</t>
@@ -2991,26 +2937,20 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J37" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v>375897</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DCVENA052SCEN</t>
@@ -3368,26 +3308,20 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J42" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>2011-01-01</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="n">
-        <v>84.03367</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDAI05VEA156NWDB</t>
@@ -3666,26 +3600,20 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J46" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="n">
-        <v>39.51449</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI01VEA156NWDB</t>
@@ -4286,26 +4214,20 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J54" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M54" s="6" t="n">
-        <v>0.0031524</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI10VEA156NWDB</t>
@@ -5155,26 +5077,20 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J65" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>1999-01-01</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="M65" s="6" t="n">
-        <v>0.0009455000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
+      <c r="M65" s="4" t="n"/>
       <c r="N65" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM09VEA156NWDB</t>
@@ -5392,26 +5308,20 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J68" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M68" s="6" t="n">
-        <v>6.326667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI02VEA156NWDB</t>
@@ -5544,26 +5454,20 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J70" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M70" s="6" t="n">
-        <v>6.681727</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="n"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI04VEA156NWDB</t>
@@ -5775,26 +5679,20 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I73" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J73" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M73" s="6" t="n">
-        <v>77.95326</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
+      <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI07VEA156NWDB</t>
@@ -5933,26 +5831,20 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J75" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>1993-01-01</t>
-        </is>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>2002-01-01</t>
-        </is>
-      </c>
-      <c r="M75" s="6" t="n">
-        <v>2.23138</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K75" s="4" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr"/>
+      <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEM01VEA156NWDB</t>
@@ -6237,26 +6129,20 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J79" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K79" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M79" s="6" t="n">
-        <v>0.722</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K79" s="4" t="inlineStr"/>
+      <c r="L79" s="4" t="inlineStr"/>
+      <c r="M79" s="4" t="n"/>
       <c r="N79" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI03VEA066NWDB</t>
@@ -6316,26 +6202,20 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J80" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>1996-01-01</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M80" s="6" t="n">
-        <v>0.390838</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI04VEA066NWDB</t>
@@ -6468,26 +6348,20 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I82" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J82" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M82" s="6" t="n">
-        <v>92.47150000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI06VEA156NWDB</t>
@@ -6784,26 +6658,20 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J86" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K86" s="4" t="inlineStr">
-        <is>
-          <t>1995-01-01</t>
-        </is>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M86" s="6" t="n">
-        <v>2.534804</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
+      <c r="M86" s="4" t="n"/>
       <c r="N86" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI10VEA156NWDB</t>
@@ -7021,26 +6889,20 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J89" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t>1995-01-01</t>
-        </is>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K89" s="4" t="inlineStr"/>
+      <c r="L89" s="4" t="inlineStr"/>
+      <c r="M89" s="4" t="n"/>
       <c r="N89" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI13VEA156NWDB</t>
@@ -7173,26 +7035,20 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J91" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M91" s="6" t="n">
-        <v>1.231569</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="n"/>
       <c r="N91" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOM01VEA644NWDB</t>
@@ -7331,26 +7187,20 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J93" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M93" s="6" t="n">
-        <v>0.83999997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K93" s="4" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr"/>
+      <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI02VEA156NWDB</t>
@@ -7410,26 +7260,20 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J94" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M94" s="6" t="n">
-        <v>10.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI03VEA156NWDB</t>
@@ -7714,26 +7558,20 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J98" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K98" s="4" t="inlineStr">
-        <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M98" s="6" t="n">
-        <v>604.0700099999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K98" s="4" t="inlineStr"/>
+      <c r="L98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="n"/>
       <c r="N98" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI07VEA156NWDB</t>
@@ -8019,7 +7857,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="n">
-        <v>6707</v>
+        <v>6711</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -8028,11 +7866,11 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>873.4614</v>
+        <v>877.9156</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
@@ -8324,26 +8162,20 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J106" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K106" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M106" s="5" t="n">
-        <v>3042</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K106" s="4" t="inlineStr"/>
+      <c r="L106" s="4" t="inlineStr"/>
+      <c r="M106" s="4" t="n"/>
       <c r="N106" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FLVENA475SCEN</t>
@@ -8403,26 +8235,20 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J107" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K107" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v>-3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K107" s="4" t="inlineStr"/>
+      <c r="L107" s="4" t="inlineStr"/>
+      <c r="M107" s="4" t="n"/>
       <c r="N107" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTAGCYNET32719</t>
@@ -8482,26 +8308,20 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I108" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J108" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="K108" s="4" t="inlineStr">
-        <is>
-          <t>1984-12-01</t>
-        </is>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M108" s="5" t="n">
-        <v>88</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K108" s="4" t="inlineStr"/>
+      <c r="L108" s="4" t="inlineStr"/>
+      <c r="M108" s="4" t="n"/>
       <c r="N108" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTAGCYPOS32719</t>
@@ -8561,26 +8381,20 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J109" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K109" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M109" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K109" s="4" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr"/>
+      <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTAGCYVALCHG32719</t>
@@ -8640,26 +8454,20 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J110" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K110" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M110" s="5" t="n">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K110" s="4" t="inlineStr"/>
+      <c r="L110" s="4" t="inlineStr"/>
+      <c r="M110" s="4" t="n"/>
       <c r="N110" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTCORPNET32719</t>
@@ -8719,26 +8527,20 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J111" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="K111" s="4" t="inlineStr">
-        <is>
-          <t>1984-12-01</t>
-        </is>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M111" s="5" t="n">
-        <v>1669</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K111" s="4" t="inlineStr"/>
+      <c r="L111" s="4" t="inlineStr"/>
+      <c r="M111" s="4" t="n"/>
       <c r="N111" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTCORPPOS32719</t>
@@ -8798,26 +8600,20 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I112" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J112" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K112" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M112" s="5" t="n">
-        <v>-24</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K112" s="4" t="inlineStr"/>
+      <c r="L112" s="4" t="inlineStr"/>
+      <c r="M112" s="4" t="n"/>
       <c r="N112" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTCORPVALCHG32719</t>
@@ -8877,26 +8673,20 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J113" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K113" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v>37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K113" s="4" t="inlineStr"/>
+      <c r="L113" s="4" t="inlineStr"/>
+      <c r="M113" s="4" t="n"/>
       <c r="N113" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTEQTYNET32719</t>
@@ -8961,7 +8751,7 @@
       </c>
       <c r="I114" s="4" t="inlineStr"/>
       <c r="J114" s="5" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
@@ -8970,11 +8760,11 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M114" s="5" t="n">
-        <v>3950</v>
+        <v>4086</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
@@ -9035,26 +8825,20 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J115" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K115" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M115" s="5" t="n">
-        <v>-36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K115" s="4" t="inlineStr"/>
+      <c r="L115" s="4" t="inlineStr"/>
+      <c r="M115" s="4" t="n"/>
       <c r="N115" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTEQTYVALCHG32719</t>
@@ -9114,26 +8898,20 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J116" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K116" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M116" s="5" t="n">
-        <v>68</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K116" s="4" t="inlineStr"/>
+      <c r="L116" s="4" t="inlineStr"/>
+      <c r="M116" s="4" t="n"/>
       <c r="N116" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTOTALNET32719</t>
@@ -9193,26 +8971,20 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J117" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="K117" s="4" t="inlineStr">
-        <is>
-          <t>1984-12-01</t>
-        </is>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M117" s="5" t="n">
-        <v>6044</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K117" s="4" t="inlineStr"/>
+      <c r="L117" s="4" t="inlineStr"/>
+      <c r="M117" s="4" t="n"/>
       <c r="N117" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTOTALPOS32719</t>
@@ -9272,26 +9044,20 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I118" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J118" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K118" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M118" s="5" t="n">
-        <v>-61</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K118" s="4" t="inlineStr"/>
+      <c r="L118" s="4" t="inlineStr"/>
+      <c r="M118" s="4" t="n"/>
       <c r="N118" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTOTALVALCHG32719</t>
@@ -9351,26 +9117,20 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J119" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K119" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M119" s="5" t="n">
-        <v>18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K119" s="4" t="inlineStr"/>
+      <c r="L119" s="4" t="inlineStr"/>
+      <c r="M119" s="4" t="n"/>
       <c r="N119" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTREASNET32719</t>
@@ -9503,26 +9263,20 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J121" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="K121" s="4" t="inlineStr">
-        <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M121" s="5" t="n">
-        <v>-1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K121" s="4" t="inlineStr"/>
+      <c r="L121" s="4" t="inlineStr"/>
+      <c r="M121" s="4" t="n"/>
       <c r="N121" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTREASVALCHG32719</t>
@@ -9587,7 +9341,7 @@
       </c>
       <c r="I122" s="4" t="inlineStr"/>
       <c r="J122" s="5" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
@@ -9596,11 +9350,11 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M122" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
         <is>
@@ -9661,26 +9415,20 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J123" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="K123" s="4" t="inlineStr">
-        <is>
-          <t>2003-02-01</t>
-        </is>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M123" s="5" t="n">
-        <v>304</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K123" s="4" t="inlineStr"/>
+      <c r="L123" s="4" t="inlineStr"/>
+      <c r="M123" s="4" t="n"/>
       <c r="N123" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORSTTREASPOS32719</t>
@@ -9745,7 +9493,7 @@
       </c>
       <c r="I124" s="4" t="inlineStr"/>
       <c r="J124" s="5" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
@@ -9754,11 +9502,11 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M124" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
@@ -9824,7 +9572,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="5" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
@@ -9833,11 +9581,11 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M125" s="5" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
         <is>
@@ -10360,26 +10108,20 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I132" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J132" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K132" s="4" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M132" s="5" t="n">
-        <v>72907</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K132" s="4" t="inlineStr"/>
+      <c r="L132" s="4" t="inlineStr"/>
+      <c r="M132" s="4" t="n"/>
       <c r="N132" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/HIVENA052SCEN</t>
@@ -10512,26 +10254,20 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I134" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J134" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="K134" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M134" s="5" t="n">
-        <v>1125646</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K134" s="4" t="inlineStr"/>
+      <c r="L134" s="4" t="inlineStr"/>
+      <c r="M134" s="4" t="n"/>
       <c r="N134" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IAVENA052SCEN</t>
@@ -10591,26 +10327,20 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J135" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K135" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M135" s="5" t="n">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K135" s="4" t="inlineStr"/>
+      <c r="L135" s="4" t="inlineStr"/>
+      <c r="M135" s="4" t="n"/>
       <c r="N135" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IAVENA475SCEN</t>
@@ -10670,26 +10400,20 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I136" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J136" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="K136" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="M136" s="6" t="n">
-        <v>0.65</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K136" s="4" t="inlineStr"/>
+      <c r="L136" s="4" t="inlineStr"/>
+      <c r="M136" s="4" t="n"/>
       <c r="N136" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IBANAINIAIVE</t>
@@ -10895,26 +10619,20 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J139" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="K139" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>2011-10-01</t>
-        </is>
-      </c>
-      <c r="M139" s="6" t="n">
-        <v>7.7885</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K139" s="4" t="inlineStr"/>
+      <c r="L139" s="4" t="inlineStr"/>
+      <c r="M139" s="4" t="n"/>
       <c r="N139" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IBANRIAIVE</t>
@@ -11047,26 +10765,20 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J141" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M141" s="6" t="n">
-        <v>-1.126</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K141" s="4" t="inlineStr"/>
+      <c r="L141" s="4" t="inlineStr"/>
+      <c r="M141" s="4" t="n"/>
       <c r="N141" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IBANRINIVE</t>
@@ -11126,26 +10838,20 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J142" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K142" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M142" s="5" t="n">
-        <v>188</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K142" s="4" t="inlineStr"/>
+      <c r="L142" s="4" t="inlineStr"/>
+      <c r="M142" s="4" t="n"/>
       <c r="N142" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ICBUSEASEXQVEN</t>
@@ -11284,26 +10990,20 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J144" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="K144" s="4" t="inlineStr">
-        <is>
-          <t>1993-07-01</t>
-        </is>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="M144" s="6" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K144" s="4" t="inlineStr"/>
+      <c r="L144" s="4" t="inlineStr"/>
+      <c r="M144" s="4" t="n"/>
       <c r="N144" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDS1MNIAOFCVE</t>
@@ -11436,26 +11136,20 @@
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J146" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="K146" s="4" t="inlineStr">
-        <is>
-          <t>1993-07-01</t>
-        </is>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="M146" s="6" t="n">
-        <v>1.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K146" s="4" t="inlineStr"/>
+      <c r="L146" s="4" t="inlineStr"/>
+      <c r="M146" s="4" t="n"/>
       <c r="N146" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDS1MNIAONCVE</t>
@@ -11740,26 +11434,20 @@
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I150" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J150" s="5" t="n">
-        <v>203</v>
-      </c>
-      <c r="K150" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M150" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K150" s="4" t="inlineStr"/>
+      <c r="L150" s="4" t="inlineStr"/>
+      <c r="M150" s="4" t="n"/>
       <c r="N150" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDS1YMAORINCVE</t>
@@ -12044,26 +11732,20 @@
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I154" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J154" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K154" s="4" t="inlineStr">
-        <is>
-          <t>1993-10-01</t>
-        </is>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>1994-04-01</t>
-        </is>
-      </c>
-      <c r="M154" s="6" t="n">
-        <v>-0.006</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K154" s="4" t="inlineStr"/>
+      <c r="L154" s="4" t="inlineStr"/>
+      <c r="M154" s="4" t="n"/>
       <c r="N154" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSBMRINIVE</t>
@@ -12202,26 +11884,20 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J156" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="K156" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L156" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M156" s="5" t="n">
-        <v>2397</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K156" s="4" t="inlineStr"/>
+      <c r="L156" s="4" t="inlineStr"/>
+      <c r="M156" s="4" t="n"/>
       <c r="N156" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMNINIVE</t>
@@ -12281,26 +11957,20 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J157" s="5" t="n">
-        <v>214</v>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M157" s="5" t="n">
-        <v>15950</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K157" s="4" t="inlineStr"/>
+      <c r="L157" s="4" t="inlineStr"/>
+      <c r="M157" s="4" t="n"/>
       <c r="N157" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMRIAOVE</t>
@@ -12585,26 +12255,20 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I161" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J161" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K161" s="4" t="inlineStr">
-        <is>
-          <t>1987-01-01</t>
-        </is>
-      </c>
-      <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="M161" s="6" t="n">
-        <v>0.74852</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K161" s="4" t="inlineStr"/>
+      <c r="L161" s="4" t="inlineStr"/>
+      <c r="M161" s="4" t="n"/>
       <c r="N161" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGFCAMNIAOVE</t>
@@ -12664,26 +12328,20 @@
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J162" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="K162" s="4" t="inlineStr">
-        <is>
-          <t>1987-04-01</t>
-        </is>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>2014-10-01</t>
-        </is>
-      </c>
-      <c r="M162" s="6" t="n">
-        <v>-0.08400000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K162" s="4" t="inlineStr"/>
+      <c r="L162" s="4" t="inlineStr"/>
+      <c r="M162" s="4" t="n"/>
       <c r="N162" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGFCAMNINIVE</t>
@@ -12743,26 +12401,20 @@
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J163" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="K163" s="4" t="inlineStr">
-        <is>
-          <t>1993-07-01</t>
-        </is>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="M163" s="6" t="n">
-        <v>32.0498</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K163" s="4" t="inlineStr"/>
+      <c r="L163" s="4" t="inlineStr"/>
+      <c r="M163" s="4" t="n"/>
       <c r="N163" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGGGAMNIAOVE</t>
@@ -12822,26 +12474,20 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J164" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="K164" s="4" t="inlineStr">
-        <is>
-          <t>1993-07-01</t>
-        </is>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M164" s="6" t="n">
-        <v>-1.12602</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K164" s="4" t="inlineStr"/>
+      <c r="L164" s="4" t="inlineStr"/>
+      <c r="M164" s="4" t="n"/>
       <c r="N164" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGGGAMNINIVE</t>
@@ -13053,26 +12699,20 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I167" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J167" s="5" t="n">
-        <v>203</v>
-      </c>
-      <c r="K167" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M167" s="5" t="n">
-        <v>4500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K167" s="4" t="inlineStr"/>
+      <c r="L167" s="4" t="inlineStr"/>
+      <c r="M167" s="4" t="n"/>
       <c r="N167" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSNFAMRIAOVE</t>
@@ -13205,26 +12845,20 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I169" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J169" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K169" s="4" t="inlineStr">
-        <is>
-          <t>1987-01-01</t>
-        </is>
-      </c>
-      <c r="L169" s="4" t="inlineStr">
-        <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="M169" s="6" t="n">
-        <v>0.64852</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K169" s="4" t="inlineStr"/>
+      <c r="L169" s="4" t="inlineStr"/>
+      <c r="M169" s="4" t="n"/>
       <c r="N169" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSOFAMRIAOVE</t>
@@ -13357,26 +12991,20 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I171" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J171" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K171" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M171" s="5" t="n">
-        <v>13776</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K171" s="4" t="inlineStr"/>
+      <c r="L171" s="4" t="inlineStr"/>
+      <c r="M171" s="4" t="n"/>
       <c r="N171" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDVENA052SCEN</t>
@@ -13436,26 +13064,20 @@
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I172" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J172" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K172" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L172" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M172" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K172" s="4" t="inlineStr"/>
+      <c r="L172" s="4" t="inlineStr"/>
+      <c r="M172" s="4" t="n"/>
       <c r="N172" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDVENA475SCEN</t>
@@ -13661,26 +13283,20 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J175" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K175" s="4" t="inlineStr">
-        <is>
-          <t>1990-10-01</t>
-        </is>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>1997-04-01</t>
-        </is>
-      </c>
-      <c r="M175" s="6" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K175" s="4" t="inlineStr"/>
+      <c r="L175" s="4" t="inlineStr"/>
+      <c r="M175" s="4" t="n"/>
       <c r="N175" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIAOVE</t>
@@ -13740,26 +13356,20 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J176" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K176" s="4" t="inlineStr">
-        <is>
-          <t>1993-10-01</t>
-        </is>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="M176" s="6" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K176" s="4" t="inlineStr"/>
+      <c r="L176" s="4" t="inlineStr"/>
+      <c r="M176" s="4" t="n"/>
       <c r="N176" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIGIVE</t>
@@ -13898,26 +13508,20 @@
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J178" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K178" s="4" t="inlineStr">
-        <is>
-          <t>1990-10-01</t>
-        </is>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>1997-04-01</t>
-        </is>
-      </c>
-      <c r="M178" s="6" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K178" s="4" t="inlineStr"/>
+      <c r="L178" s="4" t="inlineStr"/>
+      <c r="M178" s="4" t="n"/>
       <c r="N178" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMIRIAOVE</t>
@@ -13977,26 +13581,20 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I179" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J179" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K179" s="4" t="inlineStr">
-        <is>
-          <t>1993-10-01</t>
-        </is>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="M179" s="6" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K179" s="4" t="inlineStr"/>
+      <c r="L179" s="4" t="inlineStr"/>
+      <c r="M179" s="4" t="n"/>
       <c r="N179" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMIRIGIVE</t>
@@ -14281,26 +13879,20 @@
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I183" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J183" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K183" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L183" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M183" s="5" t="n">
-        <v>19</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K183" s="4" t="inlineStr"/>
+      <c r="L183" s="4" t="inlineStr"/>
+      <c r="M183" s="4" t="n"/>
       <c r="N183" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/INVENA475SCEN</t>
@@ -14439,26 +14031,20 @@
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I185" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J185" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K185" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="L185" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="M185" s="6" t="n">
-        <v>246.677206628298</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K185" s="4" t="inlineStr"/>
+      <c r="L185" s="4" t="inlineStr"/>
+      <c r="M185" s="4" t="n"/>
       <c r="N185" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ITNETSECRP6VEN</t>
@@ -14834,26 +14420,20 @@
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I190" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J190" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K190" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L190" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M190" s="5" t="n">
-        <v>1119525</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K190" s="4" t="inlineStr"/>
+      <c r="L190" s="4" t="inlineStr"/>
+      <c r="M190" s="4" t="n"/>
       <c r="N190" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KSVENA052SCEN</t>
@@ -14913,26 +14493,20 @@
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I191" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J191" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K191" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L191" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M191" s="5" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K191" s="4" t="inlineStr"/>
+      <c r="L191" s="4" t="inlineStr"/>
+      <c r="M191" s="4" t="n"/>
       <c r="N191" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KSVENA475SCEN</t>
@@ -15065,26 +14639,20 @@
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I193" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J193" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K193" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L193" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M193" s="5" t="n">
-        <v>23</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K193" s="4" t="inlineStr"/>
+      <c r="L193" s="4" t="inlineStr"/>
+      <c r="M193" s="4" t="n"/>
       <c r="N193" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KYVENA475SCEN</t>
@@ -15223,26 +14791,20 @@
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I195" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J195" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K195" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L195" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M195" s="5" t="n">
-        <v>208764595</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K195" s="4" t="inlineStr"/>
+      <c r="L195" s="4" t="inlineStr"/>
+      <c r="M195" s="4" t="n"/>
       <c r="N195" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/LAVENA052SCEN</t>
@@ -15302,26 +14864,20 @@
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I196" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J196" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K196" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L196" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M196" s="5" t="n">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K196" s="4" t="inlineStr"/>
+      <c r="L196" s="4" t="inlineStr"/>
+      <c r="M196" s="4" t="n"/>
       <c r="N196" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/LAVENA475SCEN</t>
@@ -15381,26 +14937,20 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J197" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K197" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L197" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M197" s="5" t="n">
-        <v>1854340</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K197" s="4" t="inlineStr"/>
+      <c r="L197" s="4" t="inlineStr"/>
+      <c r="M197" s="4" t="n"/>
       <c r="N197" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MAVENA052SCEN</t>
@@ -15460,26 +15010,20 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J198" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K198" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L198" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M198" s="5" t="n">
-        <v>18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K198" s="4" t="inlineStr"/>
+      <c r="L198" s="4" t="inlineStr"/>
+      <c r="M198" s="4" t="n"/>
       <c r="N198" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MAVENA475SCEN</t>
@@ -15612,26 +15156,20 @@
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I200" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J200" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K200" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M200" s="5" t="n">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K200" s="4" t="inlineStr"/>
+      <c r="L200" s="4" t="inlineStr"/>
+      <c r="M200" s="4" t="n"/>
       <c r="N200" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MDVENA475SCEN</t>
@@ -15691,26 +15229,20 @@
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I201" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J201" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K201" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L201" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M201" s="5" t="n">
-        <v>419576</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K201" s="4" t="inlineStr"/>
+      <c r="L201" s="4" t="inlineStr"/>
+      <c r="M201" s="4" t="n"/>
       <c r="N201" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MEVENA052SCEN</t>
@@ -15770,26 +15302,20 @@
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I202" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J202" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K202" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L202" s="4" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="M202" s="5" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K202" s="4" t="inlineStr"/>
+      <c r="L202" s="4" t="inlineStr"/>
+      <c r="M202" s="4" t="n"/>
       <c r="N202" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MEVENA475SCEN</t>
@@ -15849,26 +15375,20 @@
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I203" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J203" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K203" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L203" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M203" s="5" t="n">
-        <v>13590192</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K203" s="4" t="inlineStr"/>
+      <c r="L203" s="4" t="inlineStr"/>
+      <c r="M203" s="4" t="n"/>
       <c r="N203" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MIVENA052SCEN</t>
@@ -15928,26 +15448,20 @@
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I204" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J204" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K204" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L204" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M204" s="5" t="n">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K204" s="4" t="inlineStr"/>
+      <c r="L204" s="4" t="inlineStr"/>
+      <c r="M204" s="4" t="n"/>
       <c r="N204" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MIVENA475SCEN</t>
@@ -16165,26 +15679,20 @@
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I207" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J207" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K207" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L207" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M207" s="5" t="n">
-        <v>1571015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K207" s="4" t="inlineStr"/>
+      <c r="L207" s="4" t="inlineStr"/>
+      <c r="M207" s="4" t="n"/>
       <c r="N207" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MNVENA052SCEN</t>
@@ -16317,26 +15825,20 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I209" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J209" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="K209" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L209" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M209" s="5" t="n">
-        <v>758051</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K209" s="4" t="inlineStr"/>
+      <c r="L209" s="4" t="inlineStr"/>
+      <c r="M209" s="4" t="n"/>
       <c r="N209" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MOVENA052SCEN</t>
@@ -16396,26 +15898,20 @@
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J210" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K210" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L210" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M210" s="5" t="n">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K210" s="4" t="inlineStr"/>
+      <c r="L210" s="4" t="inlineStr"/>
+      <c r="M210" s="4" t="n"/>
       <c r="N210" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MOVENA475SCEN</t>
@@ -16548,26 +16044,20 @@
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I212" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J212" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K212" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L212" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M212" s="5" t="n">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K212" s="4" t="inlineStr"/>
+      <c r="L212" s="4" t="inlineStr"/>
+      <c r="M212" s="4" t="n"/>
       <c r="N212" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MSVENA475SCEN</t>
@@ -16627,26 +16117,20 @@
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I213" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J213" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K213" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L213" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M213" s="5" t="n">
-        <v>206865</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K213" s="4" t="inlineStr"/>
+      <c r="L213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="n"/>
       <c r="N213" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA052SCEN</t>
@@ -16706,26 +16190,20 @@
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I214" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J214" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K214" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L214" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M214" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K214" s="4" t="inlineStr"/>
+      <c r="L214" s="4" t="inlineStr"/>
+      <c r="M214" s="4" t="n"/>
       <c r="N214" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA475SCEN</t>
@@ -16864,26 +16342,20 @@
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I216" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J216" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K216" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L216" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M216" s="5" t="n">
-        <v>4804633</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K216" s="4" t="inlineStr"/>
+      <c r="L216" s="4" t="inlineStr"/>
+      <c r="M216" s="4" t="n"/>
       <c r="N216" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NCVENA052SCEN</t>
@@ -16943,26 +16415,20 @@
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I217" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J217" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K217" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L217" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M217" s="5" t="n">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K217" s="4" t="inlineStr"/>
+      <c r="L217" s="4" t="inlineStr"/>
+      <c r="M217" s="4" t="n"/>
       <c r="N217" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NCVENA475SCEN</t>
@@ -17241,26 +16707,20 @@
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I221" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J221" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K221" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L221" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M221" s="5" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K221" s="4" t="inlineStr"/>
+      <c r="L221" s="4" t="inlineStr"/>
+      <c r="M221" s="4" t="n"/>
       <c r="N221" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NEVENA475SCEN</t>
@@ -17320,26 +16780,20 @@
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I222" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J222" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="K222" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L222" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M222" s="5" t="n">
-        <v>153807</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K222" s="4" t="inlineStr"/>
+      <c r="L222" s="4" t="inlineStr"/>
+      <c r="M222" s="4" t="n"/>
       <c r="N222" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NHVENA052SCEN</t>
@@ -17472,26 +16926,20 @@
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I224" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J224" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K224" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L224" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M224" s="5" t="n">
-        <v>3888969</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K224" s="4" t="inlineStr"/>
+      <c r="L224" s="4" t="inlineStr"/>
+      <c r="M224" s="4" t="n"/>
       <c r="N224" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NJVENA052SCEN</t>
@@ -17551,26 +16999,20 @@
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I225" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J225" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K225" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L225" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M225" s="5" t="n">
-        <v>53</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K225" s="4" t="inlineStr"/>
+      <c r="L225" s="4" t="inlineStr"/>
+      <c r="M225" s="4" t="n"/>
       <c r="N225" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NJVENA475SCEN</t>
@@ -17630,26 +17072,20 @@
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I226" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J226" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K226" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L226" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M226" s="5" t="n">
-        <v>743939</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K226" s="4" t="inlineStr"/>
+      <c r="L226" s="4" t="inlineStr"/>
+      <c r="M226" s="4" t="n"/>
       <c r="N226" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NMVENA052SCEN</t>
@@ -17709,26 +17145,20 @@
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I227" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J227" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K227" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L227" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M227" s="5" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K227" s="4" t="inlineStr"/>
+      <c r="L227" s="4" t="inlineStr"/>
+      <c r="M227" s="4" t="n"/>
       <c r="N227" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NMVENA475SCEN</t>
@@ -17788,26 +17218,20 @@
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J228" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="K228" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L228" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M228" s="5" t="n">
-        <v>144707</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K228" s="4" t="inlineStr"/>
+      <c r="L228" s="4" t="inlineStr"/>
+      <c r="M228" s="4" t="n"/>
       <c r="N228" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NVVENA052SCEN</t>
@@ -18238,26 +17662,20 @@
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I234" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J234" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K234" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L234" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M234" s="5" t="n">
-        <v>43</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K234" s="4" t="inlineStr"/>
+      <c r="L234" s="4" t="inlineStr"/>
+      <c r="M234" s="4" t="n"/>
       <c r="N234" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OHVENA475SCEN</t>
@@ -18317,26 +17735,20 @@
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I235" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J235" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K235" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L235" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M235" s="5" t="n">
-        <v>111692</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K235" s="4" t="inlineStr"/>
+      <c r="L235" s="4" t="inlineStr"/>
+      <c r="M235" s="4" t="n"/>
       <c r="N235" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OKVENA052SCEN</t>
@@ -18396,26 +17808,20 @@
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I236" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I236" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J236" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K236" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L236" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M236" s="5" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K236" s="4" t="inlineStr"/>
+      <c r="L236" s="4" t="inlineStr"/>
+      <c r="M236" s="4" t="n"/>
       <c r="N236" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OKVENA475SCEN</t>
@@ -18779,26 +18185,20 @@
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I241" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I241" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J241" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K241" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L241" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M241" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K241" s="4" t="inlineStr"/>
+      <c r="L241" s="4" t="inlineStr"/>
+      <c r="M241" s="4" t="n"/>
       <c r="N241" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEDESIGN</t>
@@ -18858,26 +18258,20 @@
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I242" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J242" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K242" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L242" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M242" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K242" s="4" t="inlineStr"/>
+      <c r="L242" s="4" t="inlineStr"/>
+      <c r="M242" s="4" t="n"/>
       <c r="N242" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEPLANT</t>
@@ -19089,26 +18483,20 @@
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I245" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J245" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K245" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L245" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M245" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K245" s="4" t="inlineStr"/>
+      <c r="L245" s="4" t="inlineStr"/>
+      <c r="M245" s="4" t="n"/>
       <c r="N245" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEUTILITY</t>
@@ -19241,26 +18629,20 @@
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I247" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J247" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K247" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L247" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M247" s="5" t="n">
-        <v>38</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K247" s="4" t="inlineStr"/>
+      <c r="L247" s="4" t="inlineStr"/>
+      <c r="M247" s="4" t="n"/>
       <c r="N247" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PAVENA475SCEN</t>
@@ -19320,26 +18702,20 @@
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I248" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J248" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K248" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L248" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M248" s="6" t="n">
-        <v>11809.94057</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K248" s="4" t="inlineStr"/>
+      <c r="L248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="n"/>
       <c r="N248" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PC2GDPVEA620NUPN</t>
@@ -19478,26 +18854,20 @@
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I250" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J250" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K250" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L250" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M250" s="6" t="n">
-        <v>10445.85073</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K250" s="4" t="inlineStr"/>
+      <c r="L250" s="4" t="inlineStr"/>
+      <c r="M250" s="4" t="n"/>
       <c r="N250" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PCDGDPVEA620NUPN</t>
@@ -20031,26 +19401,20 @@
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I257" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J257" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K257" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L257" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M257" s="6" t="n">
-        <v>31.6201782226563</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K257" s="4" t="inlineStr"/>
+      <c r="L257" s="4" t="inlineStr"/>
+      <c r="M257" s="4" t="n"/>
       <c r="N257" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLGDPOVEA670NRUG</t>
@@ -20110,26 +19474,20 @@
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I258" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J258" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K258" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L258" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M258" s="6" t="n">
-        <v>40.4344416781944</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K258" s="4" t="inlineStr"/>
+      <c r="L258" s="4" t="inlineStr"/>
+      <c r="M258" s="4" t="n"/>
       <c r="N258" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLICPPVEA670NRUG</t>
@@ -20505,26 +19863,20 @@
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I263" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J263" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K263" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L263" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M263" s="6" t="n">
-        <v>144.0149859</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K263" s="4" t="inlineStr"/>
+      <c r="L263" s="4" t="inlineStr"/>
+      <c r="M263" s="4" t="n"/>
       <c r="N263" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOGINVEA623NUPN</t>
@@ -21291,26 +20643,20 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I273" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J273" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K273" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L273" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M273" s="5" t="n">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K273" s="4" t="inlineStr"/>
+      <c r="L273" s="4" t="inlineStr"/>
+      <c r="M273" s="4" t="n"/>
       <c r="N273" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PRVENA475SCEN</t>
@@ -22081,26 +21427,20 @@
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I283" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J283" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K283" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L283" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M283" s="6" t="n">
-        <v>25811.10218</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K283" s="4" t="inlineStr"/>
+      <c r="L283" s="4" t="inlineStr"/>
+      <c r="M283" s="4" t="n"/>
       <c r="N283" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPTEVEA629NUPN</t>
@@ -22239,26 +21579,20 @@
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I285" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I285" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J285" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K285" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L285" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M285" s="6" t="n">
-        <v>10406.06094</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K285" s="4" t="inlineStr"/>
+      <c r="L285" s="4" t="inlineStr"/>
+      <c r="M285" s="4" t="n"/>
       <c r="N285" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPTTVEA625NUPN</t>
@@ -22318,26 +21652,20 @@
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I286" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J286" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K286" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L286" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M286" s="6" t="n">
-        <v>19511.40489</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K286" s="4" t="inlineStr"/>
+      <c r="L286" s="4" t="inlineStr"/>
+      <c r="M286" s="4" t="n"/>
       <c r="N286" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPWOVEA627NUPN</t>
@@ -22397,26 +21725,20 @@
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I287" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I287" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J287" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K287" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L287" s="4" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="M287" s="5" t="n">
-        <v>281736</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K287" s="4" t="inlineStr"/>
+      <c r="L287" s="4" t="inlineStr"/>
+      <c r="M287" s="4" t="n"/>
       <c r="N287" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RIVENA052SCEN</t>
@@ -22476,26 +21798,20 @@
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I288" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I288" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J288" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="K288" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L288" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M288" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K288" s="4" t="inlineStr"/>
+      <c r="L288" s="4" t="inlineStr"/>
+      <c r="M288" s="4" t="n"/>
       <c r="N288" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RIVENA475SCEN</t>
@@ -22713,26 +22029,20 @@
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I291" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I291" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J291" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K291" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L291" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M291" s="5" t="n">
-        <v>15077425</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K291" s="4" t="inlineStr"/>
+      <c r="L291" s="4" t="inlineStr"/>
+      <c r="M291" s="4" t="n"/>
       <c r="N291" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SCVENA052SCEN</t>
@@ -22792,26 +22102,20 @@
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I292" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I292" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J292" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K292" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L292" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M292" s="5" t="n">
-        <v>23</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K292" s="4" t="inlineStr"/>
+      <c r="L292" s="4" t="inlineStr"/>
+      <c r="M292" s="4" t="n"/>
       <c r="N292" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SCVENA475SCEN</t>
@@ -22944,26 +22248,20 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I294" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I294" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J294" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K294" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L294" s="4" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="M294" s="5" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K294" s="4" t="inlineStr"/>
+      <c r="L294" s="4" t="inlineStr"/>
+      <c r="M294" s="4" t="n"/>
       <c r="N294" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SDVENA475SCEN</t>
@@ -23175,26 +22473,20 @@
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I297" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I297" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J297" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="K297" s="4" t="inlineStr">
-        <is>
-          <t>1971-01-01</t>
-        </is>
-      </c>
-      <c r="L297" s="4" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M297" s="6" t="n">
-        <v>1.0806200504303</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K297" s="4" t="inlineStr"/>
+      <c r="L297" s="4" t="inlineStr"/>
+      <c r="M297" s="4" t="n"/>
       <c r="N297" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRSECOFMZSVEN</t>
@@ -23254,26 +22546,20 @@
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I298" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J298" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K298" s="4" t="inlineStr">
-        <is>
-          <t>1986-01-01</t>
-        </is>
-      </c>
-      <c r="L298" s="4" t="inlineStr">
-        <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="M298" s="6" t="n">
-        <v>1.40991997718811</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K298" s="4" t="inlineStr"/>
+      <c r="L298" s="4" t="inlineStr"/>
+      <c r="M298" s="4" t="n"/>
       <c r="N298" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRTERTFMZSVEN</t>
@@ -23728,26 +23014,20 @@
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I304" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I304" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J304" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K304" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L304" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M304" s="5" t="n">
-        <v>1404448</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K304" s="4" t="inlineStr"/>
+      <c r="L304" s="4" t="inlineStr"/>
+      <c r="M304" s="4" t="n"/>
       <c r="N304" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SMPOPTOTLVEN</t>
@@ -24202,26 +23482,20 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I310" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I310" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J310" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="K310" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L310" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="M310" s="6" t="n">
-        <v>24.9159954154898</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K310" s="4" t="inlineStr"/>
+      <c r="L310" s="4" t="inlineStr"/>
+      <c r="M310" s="4" t="n"/>
       <c r="N310" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPPOP0014TOZSVEN</t>
@@ -24737,26 +24011,20 @@
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I317" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I317" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J317" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K317" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L317" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M317" s="5" t="n">
-        <v>297118823</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K317" s="4" t="inlineStr"/>
+      <c r="L317" s="4" t="inlineStr"/>
+      <c r="M317" s="4" t="n"/>
       <c r="N317" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/TXVENA052SCEN</t>
@@ -24816,26 +24084,20 @@
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I318" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I318" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J318" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K318" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L318" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M318" s="5" t="n">
-        <v>169</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K318" s="4" t="inlineStr"/>
+      <c r="L318" s="4" t="inlineStr"/>
+      <c r="M318" s="4" t="n"/>
       <c r="N318" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/TXVENA475SCEN</t>
@@ -24895,26 +24157,20 @@
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I319" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I319" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J319" s="5" t="n">
-        <v>388</v>
-      </c>
-      <c r="K319" s="4" t="inlineStr">
-        <is>
-          <t>1994-04-01</t>
-        </is>
-      </c>
-      <c r="L319" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M319" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K319" s="4" t="inlineStr"/>
+      <c r="L319" s="4" t="inlineStr"/>
+      <c r="M319" s="4" t="n"/>
       <c r="N319" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTBONDNET32719</t>
@@ -24974,26 +24230,20 @@
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I320" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I320" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J320" s="5" t="n">
-        <v>389</v>
-      </c>
-      <c r="K320" s="4" t="inlineStr">
-        <is>
-          <t>1994-03-01</t>
-        </is>
-      </c>
-      <c r="L320" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M320" s="5" t="n">
-        <v>4989</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K320" s="4" t="inlineStr"/>
+      <c r="L320" s="4" t="inlineStr"/>
+      <c r="M320" s="4" t="n"/>
       <c r="N320" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTBONDPOS32719</t>
@@ -25053,26 +24303,20 @@
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I321" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I321" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J321" s="5" t="n">
-        <v>388</v>
-      </c>
-      <c r="K321" s="4" t="inlineStr">
-        <is>
-          <t>1994-04-01</t>
-        </is>
-      </c>
-      <c r="L321" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M321" s="5" t="n">
-        <v>35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K321" s="4" t="inlineStr"/>
+      <c r="L321" s="4" t="inlineStr"/>
+      <c r="M321" s="4" t="n"/>
       <c r="N321" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTBONDVALCHG32719</t>
@@ -25132,26 +24376,20 @@
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I322" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I322" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J322" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="K322" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="L322" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M322" s="5" t="n">
-        <v>37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K322" s="4" t="inlineStr"/>
+      <c r="L322" s="4" t="inlineStr"/>
+      <c r="M322" s="4" t="n"/>
       <c r="N322" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTCORPBONDNET32719</t>
@@ -25216,7 +24454,7 @@
       </c>
       <c r="I323" s="4" t="inlineStr"/>
       <c r="J323" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K323" s="4" t="inlineStr">
         <is>
@@ -25225,11 +24463,11 @@
       </c>
       <c r="L323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M323" s="5" t="n">
-        <v>2613</v>
+        <v>2828</v>
       </c>
       <c r="N323" s="4" t="inlineStr">
         <is>
@@ -25290,26 +24528,20 @@
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I324" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I324" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J324" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="K324" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="L324" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M324" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K324" s="4" t="inlineStr"/>
+      <c r="L324" s="4" t="inlineStr"/>
+      <c r="M324" s="4" t="n"/>
       <c r="N324" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTCORPBONDVALCHG32719</t>
@@ -25374,7 +24606,7 @@
       </c>
       <c r="I325" s="4" t="inlineStr"/>
       <c r="J325" s="5" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K325" s="4" t="inlineStr">
         <is>
@@ -25383,7 +24615,7 @@
       </c>
       <c r="L325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M325" s="5" t="n">
@@ -25448,26 +24680,20 @@
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I326" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I326" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J326" s="5" t="n">
-        <v>389</v>
-      </c>
-      <c r="K326" s="4" t="inlineStr">
-        <is>
-          <t>1994-03-01</t>
-        </is>
-      </c>
-      <c r="L326" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M326" s="5" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K326" s="4" t="inlineStr"/>
+      <c r="L326" s="4" t="inlineStr"/>
+      <c r="M326" s="4" t="n"/>
       <c r="N326" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTEQTYPOS32719</t>
@@ -25527,26 +24753,20 @@
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I327" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I327" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J327" s="5" t="n">
-        <v>388</v>
-      </c>
-      <c r="K327" s="4" t="inlineStr">
-        <is>
-          <t>1994-04-01</t>
-        </is>
-      </c>
-      <c r="L327" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M327" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K327" s="4" t="inlineStr"/>
+      <c r="L327" s="4" t="inlineStr"/>
+      <c r="M327" s="4" t="n"/>
       <c r="N327" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTEQTYVALCHG32719</t>
@@ -25606,26 +24826,20 @@
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I328" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I328" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J328" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="K328" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="L328" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M328" s="5" t="n">
-        <v>-37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K328" s="4" t="inlineStr"/>
+      <c r="L328" s="4" t="inlineStr"/>
+      <c r="M328" s="4" t="n"/>
       <c r="N328" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTGOVTBONDNET32719</t>
@@ -25685,26 +24899,20 @@
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I329" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I329" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J329" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="K329" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="L329" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M329" s="5" t="n">
-        <v>2376</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K329" s="4" t="inlineStr"/>
+      <c r="L329" s="4" t="inlineStr"/>
+      <c r="M329" s="4" t="n"/>
       <c r="N329" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTGOVTBONDPOS32719</t>
@@ -25764,26 +24972,20 @@
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I330" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I330" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J330" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="K330" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="L330" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M330" s="5" t="n">
-        <v>34</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K330" s="4" t="inlineStr"/>
+      <c r="L330" s="4" t="inlineStr"/>
+      <c r="M330" s="4" t="n"/>
       <c r="N330" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTGOVTBONDVALCHG32719</t>
@@ -25843,26 +25045,20 @@
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I331" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I331" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J331" s="5" t="n">
-        <v>388</v>
-      </c>
-      <c r="K331" s="4" t="inlineStr">
-        <is>
-          <t>1994-04-01</t>
-        </is>
-      </c>
-      <c r="L331" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M331" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K331" s="4" t="inlineStr"/>
+      <c r="L331" s="4" t="inlineStr"/>
+      <c r="M331" s="4" t="n"/>
       <c r="N331" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALNET32719</t>
@@ -25922,26 +25118,20 @@
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I332" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I332" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J332" s="5" t="n">
-        <v>389</v>
-      </c>
-      <c r="K332" s="4" t="inlineStr">
-        <is>
-          <t>1994-03-01</t>
-        </is>
-      </c>
-      <c r="L332" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M332" s="5" t="n">
-        <v>4996</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K332" s="4" t="inlineStr"/>
+      <c r="L332" s="4" t="inlineStr"/>
+      <c r="M332" s="4" t="n"/>
       <c r="N332" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALPOS32719</t>
@@ -26001,26 +25191,20 @@
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I333" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I333" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J333" s="5" t="n">
-        <v>388</v>
-      </c>
-      <c r="K333" s="4" t="inlineStr">
-        <is>
-          <t>1994-04-01</t>
-        </is>
-      </c>
-      <c r="L333" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M333" s="5" t="n">
-        <v>35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K333" s="4" t="inlineStr"/>
+      <c r="L333" s="4" t="inlineStr"/>
+      <c r="M333" s="4" t="n"/>
       <c r="N333" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALVALCHG32719</t>
@@ -26080,26 +25264,20 @@
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I334" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I334" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J334" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K334" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L334" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M334" s="5" t="n">
-        <v>910607</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K334" s="4" t="inlineStr"/>
+      <c r="L334" s="4" t="inlineStr"/>
+      <c r="M334" s="4" t="n"/>
       <c r="N334" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/UTVENA052SCEN</t>
@@ -26159,26 +25337,20 @@
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I335" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I335" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J335" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K335" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L335" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M335" s="5" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K335" s="4" t="inlineStr"/>
+      <c r="L335" s="4" t="inlineStr"/>
+      <c r="M335" s="4" t="n"/>
       <c r="N335" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/UTVENA475SCEN</t>
@@ -26311,26 +25483,20 @@
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J337" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M337" s="5" t="n">
-        <v>19</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K337" s="4" t="inlineStr"/>
+      <c r="L337" s="4" t="inlineStr"/>
+      <c r="M337" s="4" t="n"/>
       <c r="N337" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VAVENA475SCEN</t>
@@ -26536,26 +25702,20 @@
       </c>
       <c r="H340" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I340" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I340" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J340" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K340" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L340" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M340" s="5" t="n">
-        <v>10429</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K340" s="4" t="inlineStr"/>
+      <c r="L340" s="4" t="inlineStr"/>
+      <c r="M340" s="4" t="n"/>
       <c r="N340" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCACNUM</t>
@@ -26615,26 +25775,20 @@
       </c>
       <c r="H341" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I341" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I341" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J341" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K341" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L341" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M341" s="6" t="n">
-        <v>11.8235927668</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K341" s="4" t="inlineStr"/>
+      <c r="L341" s="4" t="inlineStr"/>
+      <c r="M341" s="4" t="n"/>
       <c r="N341" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAKNUM</t>
@@ -26694,26 +25848,20 @@
       </c>
       <c r="H342" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I342" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I342" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J342" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K342" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L342" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M342" s="6" t="n">
-        <v>1442.4719851783</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K342" s="4" t="inlineStr"/>
+      <c r="L342" s="4" t="inlineStr"/>
+      <c r="M342" s="4" t="n"/>
       <c r="N342" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODCANUM</t>
@@ -26773,26 +25921,20 @@
       </c>
       <c r="H343" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I343" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I343" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J343" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K343" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L343" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M343" s="5" t="n">
-        <v>31695711</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K343" s="4" t="inlineStr"/>
+      <c r="L343" s="4" t="inlineStr"/>
+      <c r="M343" s="4" t="n"/>
       <c r="N343" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODCNUM</t>
@@ -26852,26 +25994,20 @@
       </c>
       <c r="H344" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I344" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I344" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J344" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K344" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L344" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M344" s="5" t="n">
-        <v>21794</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K344" s="4" t="inlineStr"/>
+      <c r="L344" s="4" t="inlineStr"/>
+      <c r="M344" s="4" t="n"/>
       <c r="N344" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODDNUM</t>
@@ -26931,26 +26067,20 @@
       </c>
       <c r="H345" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I345" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I345" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J345" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K345" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L345" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M345" s="5" t="n">
-        <v>270382</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K345" s="4" t="inlineStr"/>
+      <c r="L345" s="4" t="inlineStr"/>
+      <c r="M345" s="4" t="n"/>
       <c r="N345" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODMFNUM</t>
@@ -27089,26 +26219,20 @@
       </c>
       <c r="H347" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I347" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I347" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J347" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K347" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L347" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M347" s="5" t="n">
-        <v>536976</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K347" s="4" t="inlineStr"/>
+      <c r="L347" s="4" t="inlineStr"/>
+      <c r="M347" s="4" t="n"/>
       <c r="N347" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAOFILPNUM</t>
@@ -27460,26 +26584,20 @@
       </c>
       <c r="H352" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I352" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I352" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J352" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K352" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L352" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M352" s="5" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K352" s="4" t="inlineStr"/>
+      <c r="L352" s="4" t="inlineStr"/>
+      <c r="M352" s="4" t="n"/>
       <c r="N352" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODDLNUM</t>
@@ -27539,26 +26657,20 @@
       </c>
       <c r="H353" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I353" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I353" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J353" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K353" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L353" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M353" s="5" t="n">
-        <v>32</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K353" s="4" t="inlineStr"/>
+      <c r="L353" s="4" t="inlineStr"/>
+      <c r="M353" s="4" t="n"/>
       <c r="N353" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODDNUM</t>
@@ -27618,26 +26730,20 @@
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I354" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I354" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J354" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K354" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L354" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M354" s="6" t="n">
-        <v>0.130378096</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K354" s="4" t="inlineStr"/>
+      <c r="L354" s="4" t="inlineStr"/>
+      <c r="M354" s="4" t="n"/>
       <c r="N354" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODMFKNUM</t>
@@ -27697,26 +26803,20 @@
       </c>
       <c r="H355" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I355" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I355" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J355" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K355" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L355" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M355" s="5" t="n">
-        <v>47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K355" s="4" t="inlineStr"/>
+      <c r="L355" s="4" t="inlineStr"/>
+      <c r="M355" s="4" t="n"/>
       <c r="N355" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODMFLNUM</t>
@@ -27849,26 +26949,20 @@
       </c>
       <c r="H357" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I357" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I357" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J357" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K357" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L357" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M357" s="6" t="n">
-        <v>1889.1919863706</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K357" s="4" t="inlineStr"/>
+      <c r="L357" s="4" t="inlineStr"/>
+      <c r="M357" s="4" t="n"/>
       <c r="N357" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCANUM</t>
@@ -27928,26 +27022,20 @@
       </c>
       <c r="H358" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I358" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I358" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J358" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K358" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L358" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M358" s="6" t="n">
-        <v>1119.62371720568</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K358" s="4" t="inlineStr"/>
+      <c r="L358" s="4" t="inlineStr"/>
+      <c r="M358" s="4" t="n"/>
       <c r="N358" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCHANUM</t>
@@ -28086,26 +27174,20 @@
       </c>
       <c r="H360" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I360" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I360" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J360" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K360" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L360" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M360" s="5" t="n">
-        <v>41472676</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K360" s="4" t="inlineStr"/>
+      <c r="L360" s="4" t="inlineStr"/>
+      <c r="M360" s="4" t="n"/>
       <c r="N360" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCPENUM</t>
@@ -28165,26 +27247,20 @@
       </c>
       <c r="H361" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I361" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I361" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J361" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K361" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L361" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M361" s="6" t="n">
-        <v>481500.416666667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K361" s="4" t="inlineStr"/>
+      <c r="L361" s="4" t="inlineStr"/>
+      <c r="M361" s="4" t="n"/>
       <c r="N361" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPENUM</t>
@@ -28244,26 +27320,20 @@
       </c>
       <c r="H362" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I362" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I362" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J362" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K362" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L362" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M362" s="6" t="n">
-        <v>66.83665774000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K362" s="4" t="inlineStr"/>
+      <c r="L362" s="4" t="inlineStr"/>
+      <c r="M362" s="4" t="n"/>
       <c r="N362" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPNUM</t>
@@ -28396,26 +27466,20 @@
       </c>
       <c r="H364" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I364" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I364" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J364" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K364" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L364" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M364" s="5" t="n">
-        <v>4202016</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K364" s="4" t="inlineStr"/>
+      <c r="L364" s="4" t="inlineStr"/>
+      <c r="M364" s="4" t="n"/>
       <c r="N364" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDOFINPPENUM</t>
@@ -28554,26 +27618,20 @@
       </c>
       <c r="H366" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I366" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I366" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J366" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K366" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L366" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M366" s="5" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K366" s="4" t="inlineStr"/>
+      <c r="L366" s="4" t="inlineStr"/>
+      <c r="M366" s="4" t="n"/>
       <c r="N366" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIODDNUM</t>
@@ -28633,26 +27691,20 @@
       </c>
       <c r="H367" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I367" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I367" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J367" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K367" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L367" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M367" s="5" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K367" s="4" t="inlineStr"/>
+      <c r="L367" s="4" t="inlineStr"/>
+      <c r="M367" s="4" t="n"/>
       <c r="N367" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIODMFNUM</t>
@@ -28712,26 +27764,20 @@
       </c>
       <c r="H368" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I368" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I368" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J368" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K368" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L368" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M368" s="5" t="n">
-        <v>48</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K368" s="4" t="inlineStr"/>
+      <c r="L368" s="4" t="inlineStr"/>
+      <c r="M368" s="4" t="n"/>
       <c r="N368" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIOFINUM</t>
@@ -28791,26 +27837,20 @@
       </c>
       <c r="H369" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I369" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I369" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J369" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K369" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L369" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M369" s="6" t="n">
-        <v>68.50582168130001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K369" s="4" t="inlineStr"/>
+      <c r="L369" s="4" t="inlineStr"/>
+      <c r="M369" s="4" t="n"/>
       <c r="N369" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCGGDPPT</t>
@@ -28870,26 +27910,20 @@
       </c>
       <c r="H370" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I370" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I370" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J370" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K370" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L370" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M370" s="6" t="n">
-        <v>23.7831197319</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K370" s="4" t="inlineStr"/>
+      <c r="L370" s="4" t="inlineStr"/>
+      <c r="M370" s="4" t="n"/>
       <c r="N370" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCHGGDPPT</t>
@@ -28949,26 +27983,20 @@
       </c>
       <c r="H371" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I371" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I371" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J371" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K371" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L371" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M371" s="6" t="n">
-        <v>1451895895202.22</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K371" s="4" t="inlineStr"/>
+      <c r="L371" s="4" t="inlineStr"/>
+      <c r="M371" s="4" t="n"/>
       <c r="N371" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCHXDC</t>
@@ -29028,26 +28056,20 @@
       </c>
       <c r="H372" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I372" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I372" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J372" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K372" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L372" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M372" s="6" t="n">
-        <v>21.4396202031903</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K372" s="4" t="inlineStr"/>
+      <c r="L372" s="4" t="inlineStr"/>
+      <c r="M372" s="4" t="n"/>
       <c r="N372" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCSGGDPPT</t>
@@ -29107,26 +28129,20 @@
       </c>
       <c r="H373" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I373" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I373" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J373" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K373" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L373" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M373" s="6" t="n">
-        <v>481500416666.6671</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K373" s="4" t="inlineStr"/>
+      <c r="L373" s="4" t="inlineStr"/>
+      <c r="M373" s="4" t="n"/>
       <c r="N373" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCSXDC</t>
@@ -29259,26 +28275,20 @@
       </c>
       <c r="H375" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I375" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I375" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J375" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K375" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L375" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M375" s="6" t="n">
-        <v>2531710068.02</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K375" s="4" t="inlineStr"/>
+      <c r="L375" s="4" t="inlineStr"/>
+      <c r="M375" s="4" t="n"/>
       <c r="N375" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODDXDC</t>
@@ -29338,26 +28348,20 @@
       </c>
       <c r="H376" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I376" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I376" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J376" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K376" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L376" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M376" s="6" t="n">
-        <v>37322701822.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K376" s="4" t="inlineStr"/>
+      <c r="L376" s="4" t="inlineStr"/>
+      <c r="M376" s="4" t="n"/>
       <c r="N376" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODMFXDC</t>
@@ -29417,26 +28421,20 @@
       </c>
       <c r="H377" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I377" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I377" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J377" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K377" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L377" s="4" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="M377" s="5" t="n">
-        <v>359000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K377" s="4" t="inlineStr"/>
+      <c r="L377" s="4" t="inlineStr"/>
+      <c r="M377" s="4" t="n"/>
       <c r="N377" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLOFILPXDC</t>
@@ -29800,26 +28798,20 @@
       </c>
       <c r="H382" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I382" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I382" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J382" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K382" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L382" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M382" s="5" t="n">
-        <v>5466</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K382" s="4" t="inlineStr"/>
+      <c r="L382" s="4" t="inlineStr"/>
+      <c r="M382" s="4" t="n"/>
       <c r="N382" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODDNUM</t>
@@ -29879,26 +28871,20 @@
       </c>
       <c r="H383" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I383" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I383" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J383" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K383" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L383" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M383" s="5" t="n">
-        <v>42341</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K383" s="4" t="inlineStr"/>
+      <c r="L383" s="4" t="inlineStr"/>
+      <c r="M383" s="4" t="n"/>
       <c r="N383" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODMFNUM</t>
@@ -30031,26 +29017,20 @@
       </c>
       <c r="H385" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I385" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I385" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J385" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K385" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L385" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M385" s="6" t="n">
-        <v>336.987464420657</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K385" s="4" t="inlineStr"/>
+      <c r="L385" s="4" t="inlineStr"/>
+      <c r="M385" s="4" t="n"/>
       <c r="N385" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHANUM</t>
@@ -30110,26 +29090,20 @@
       </c>
       <c r="H386" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I386" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I386" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J386" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K386" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L386" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M386" s="6" t="n">
-        <v>7404689.58333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K386" s="4" t="inlineStr"/>
+      <c r="L386" s="4" t="inlineStr"/>
+      <c r="M386" s="4" t="n"/>
       <c r="N386" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHPENUM</t>
@@ -30335,26 +29309,20 @@
       </c>
       <c r="H389" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I389" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I389" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J389" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K389" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L389" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M389" s="6" t="n">
-        <v>41.2593449</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K389" s="4" t="inlineStr"/>
+      <c r="L389" s="4" t="inlineStr"/>
+      <c r="M389" s="4" t="n"/>
       <c r="N389" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCSPNUM</t>
@@ -30414,26 +29382,20 @@
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I390" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I390" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J390" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K390" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L390" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M390" s="6" t="n">
-        <v>37.8908354029</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K390" s="4" t="inlineStr"/>
+      <c r="L390" s="4" t="inlineStr"/>
+      <c r="M390" s="4" t="n"/>
       <c r="N390" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCGGDPPT</t>
@@ -30645,26 +29607,20 @@
       </c>
       <c r="H393" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I393" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I393" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J393" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K393" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L393" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M393" s="6" t="n">
-        <v>2437538671645.28</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K393" s="4" t="inlineStr"/>
+      <c r="L393" s="4" t="inlineStr"/>
+      <c r="M393" s="4" t="n"/>
       <c r="N393" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCXDC</t>
@@ -30724,26 +29680,20 @@
       </c>
       <c r="H394" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I394" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I394" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J394" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K394" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L394" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M394" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K394" s="4" t="inlineStr"/>
+      <c r="L394" s="4" t="inlineStr"/>
+      <c r="M394" s="4" t="n"/>
       <c r="N394" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODDSXDC</t>
@@ -30803,26 +29753,20 @@
       </c>
       <c r="H395" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I395" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I395" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J395" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K395" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L395" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M395" s="6" t="n">
-        <v>1878132857.56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K395" s="4" t="inlineStr"/>
+      <c r="L395" s="4" t="inlineStr"/>
+      <c r="M395" s="4" t="n"/>
       <c r="N395" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODDXDC</t>
@@ -30882,26 +29826,20 @@
       </c>
       <c r="H396" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I396" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I396" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J396" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K396" s="4" t="inlineStr">
-        <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="L396" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M396" s="5" t="n">
-        <v>10753000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K396" s="4" t="inlineStr"/>
+      <c r="L396" s="4" t="inlineStr"/>
+      <c r="M396" s="4" t="n"/>
       <c r="N396" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFSXDC</t>
@@ -30961,26 +29899,20 @@
       </c>
       <c r="H397" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I397" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I397" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J397" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K397" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L397" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M397" s="6" t="n">
-        <v>27106310381.76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K397" s="4" t="inlineStr"/>
+      <c r="L397" s="4" t="inlineStr"/>
+      <c r="M397" s="4" t="n"/>
       <c r="N397" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFXDC</t>
@@ -31119,26 +30051,20 @@
       </c>
       <c r="H399" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I399" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I399" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J399" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K399" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L399" s="4" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="M399" s="5" t="n">
-        <v>466033</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K399" s="4" t="inlineStr"/>
+      <c r="L399" s="4" t="inlineStr"/>
+      <c r="M399" s="4" t="n"/>
       <c r="N399" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VTVENA052SCEN</t>
@@ -31271,26 +30197,20 @@
       </c>
       <c r="H401" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I401" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I401" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J401" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K401" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L401" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M401" s="5" t="n">
-        <v>2501814</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K401" s="4" t="inlineStr"/>
+      <c r="L401" s="4" t="inlineStr"/>
+      <c r="M401" s="4" t="n"/>
       <c r="N401" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WAVENA052SCEN</t>
@@ -31350,26 +30270,20 @@
       </c>
       <c r="H402" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I402" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I402" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J402" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K402" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L402" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M402" s="5" t="n">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K402" s="4" t="inlineStr"/>
+      <c r="L402" s="4" t="inlineStr"/>
+      <c r="M402" s="4" t="n"/>
       <c r="N402" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WAVENA475SCEN</t>
@@ -31429,26 +30343,20 @@
       </c>
       <c r="H403" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I403" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I403" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J403" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K403" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L403" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M403" s="5" t="n">
-        <v>2392941</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K403" s="4" t="inlineStr"/>
+      <c r="L403" s="4" t="inlineStr"/>
+      <c r="M403" s="4" t="n"/>
       <c r="N403" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WIVENA052SCEN</t>
@@ -31508,26 +30416,20 @@
       </c>
       <c r="H404" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I404" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I404" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J404" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K404" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L404" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M404" s="5" t="n">
-        <v>29</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K404" s="4" t="inlineStr"/>
+      <c r="L404" s="4" t="inlineStr"/>
+      <c r="M404" s="4" t="n"/>
       <c r="N404" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WIVENA475SCEN</t>
@@ -31660,26 +30562,20 @@
       </c>
       <c r="H406" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I406" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I406" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J406" s="5" t="n">
-        <v>290</v>
-      </c>
-      <c r="K406" s="4" t="inlineStr">
-        <is>
-          <t>1954-01-01</t>
-        </is>
-      </c>
-      <c r="L406" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M406" s="6" t="n">
-        <v>0.269383</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K406" s="4" t="inlineStr"/>
+      <c r="L406" s="4" t="inlineStr"/>
+      <c r="M406" s="4" t="n"/>
       <c r="N406" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WUIMAVEN</t>
@@ -31744,7 +30640,7 @@
       </c>
       <c r="I407" s="4" t="inlineStr"/>
       <c r="J407" s="5" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K407" s="4" t="inlineStr">
         <is>
@@ -31753,11 +30649,11 @@
       </c>
       <c r="L407" s="4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M407" s="6" t="n">
-        <v>0.6480882</v>
+        <v>0.7686395</v>
       </c>
       <c r="N407" s="4" t="inlineStr">
         <is>
@@ -31818,26 +30714,20 @@
       </c>
       <c r="H408" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I408" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I408" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J408" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="K408" s="4" t="inlineStr">
-        <is>
-          <t>1996-01-01</t>
-        </is>
-      </c>
-      <c r="L408" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M408" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K408" s="4" t="inlineStr"/>
+      <c r="L408" s="4" t="inlineStr"/>
+      <c r="M408" s="4" t="n"/>
       <c r="N408" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WUPIVEN</t>
@@ -32049,26 +30939,20 @@
       </c>
       <c r="H411" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I411" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I411" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J411" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K411" s="4" t="inlineStr">
-        <is>
-          <t>2011-01-01</t>
-        </is>
-      </c>
-      <c r="L411" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M411" s="5" t="n">
-        <v>43832725</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K411" s="4" t="inlineStr"/>
+      <c r="L411" s="4" t="inlineStr"/>
+      <c r="M411" s="4" t="n"/>
       <c r="N411" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WYVENA052SCEN</t>
@@ -32322,7 +31206,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -32379,7 +31263,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>318</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15">
@@ -32389,7 +31273,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>31840</v>
+        <v>16776</v>
       </c>
     </row>
   </sheetData>
